--- a/static/sample-data/synth_otc_pharma.xlsx
+++ b/static/sample-data/synth_otc_pharma.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Данные" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>date</t>
   </si>
@@ -25,7 +25,7 @@
     <t>tv_trp</t>
   </si>
   <si>
-    <t>apteka_ooh_ots</t>
+    <t>apteka_ooh_contacts</t>
   </si>
   <si>
     <t>digital_spend</t>
@@ -40,10 +40,7 @@
     <t>weather_temp_low</t>
   </si>
   <si>
-    <t>holiday_newyear_preshop</t>
-  </si>
-  <si>
-    <t>avg_temp</t>
+    <t>holiday_newyear</t>
   </si>
 </sst>
 </file>
@@ -379,10 +376,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -410,31 +407,28 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>44592</v>
       </c>
       <c r="B2">
-        <v>139004</v>
+        <v>134278</v>
       </c>
       <c r="C2">
-        <v>306.3</v>
+        <v>257.2</v>
       </c>
       <c r="D2">
-        <v>2004503</v>
+        <v>2799296</v>
       </c>
       <c r="E2">
-        <v>3754097</v>
+        <v>2455759</v>
       </c>
       <c r="F2">
-        <v>268525</v>
+        <v>113160</v>
       </c>
       <c r="G2">
-        <v>324.3</v>
+        <v>227.8</v>
       </c>
       <c r="H2">
         <v>4.28</v>
@@ -442,31 +436,28 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>44620</v>
       </c>
       <c r="B3">
-        <v>146831</v>
+        <v>143809</v>
       </c>
       <c r="C3">
-        <v>90.8</v>
+        <v>58.4</v>
       </c>
       <c r="D3">
-        <v>924327</v>
+        <v>808876</v>
       </c>
       <c r="E3">
-        <v>3122140</v>
+        <v>3528676</v>
       </c>
       <c r="F3">
-        <v>238662</v>
+        <v>143241</v>
       </c>
       <c r="G3">
-        <v>70.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="H3">
         <v>6.05</v>
@@ -474,31 +465,28 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
-        <v>-6.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>44651</v>
       </c>
       <c r="B4">
-        <v>125083</v>
+        <v>122774</v>
       </c>
       <c r="C4">
-        <v>84.40000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="D4">
-        <v>2096467</v>
+        <v>2394175</v>
       </c>
       <c r="E4">
-        <v>1304621</v>
+        <v>914663</v>
       </c>
       <c r="F4">
-        <v>174357</v>
+        <v>359245</v>
       </c>
       <c r="G4">
-        <v>305.4</v>
+        <v>300.3</v>
       </c>
       <c r="H4">
         <v>3.8</v>
@@ -506,31 +494,28 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>44681</v>
       </c>
       <c r="B5">
-        <v>121311</v>
+        <v>121297</v>
       </c>
       <c r="C5">
-        <v>237.1</v>
+        <v>311.6</v>
       </c>
       <c r="D5">
-        <v>1449336</v>
+        <v>1068395</v>
       </c>
       <c r="E5">
-        <v>1081590</v>
+        <v>1074130</v>
       </c>
       <c r="F5">
-        <v>183480</v>
+        <v>489336</v>
       </c>
       <c r="G5">
-        <v>155.4</v>
+        <v>193.9</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -538,31 +523,28 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>44712</v>
       </c>
       <c r="B6">
-        <v>105710</v>
+        <v>108488</v>
       </c>
       <c r="C6">
-        <v>105.1</v>
+        <v>163.7</v>
       </c>
       <c r="D6">
-        <v>527289</v>
+        <v>581067</v>
       </c>
       <c r="E6">
-        <v>3149362</v>
+        <v>4117782</v>
       </c>
       <c r="F6">
-        <v>301011</v>
+        <v>142338</v>
       </c>
       <c r="G6">
-        <v>287.4</v>
+        <v>380.7</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -570,31 +552,28 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>44742</v>
       </c>
       <c r="B7">
-        <v>118819</v>
+        <v>121199</v>
       </c>
       <c r="C7">
-        <v>68.3</v>
+        <v>125.4</v>
       </c>
       <c r="D7">
-        <v>1051659</v>
+        <v>1151655</v>
       </c>
       <c r="E7">
-        <v>2273186</v>
+        <v>2163899</v>
       </c>
       <c r="F7">
-        <v>273845</v>
+        <v>301538</v>
       </c>
       <c r="G7">
-        <v>90.40000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -602,31 +581,28 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>44773</v>
       </c>
       <c r="B8">
-        <v>113568</v>
+        <v>111728</v>
       </c>
       <c r="C8">
-        <v>133.8</v>
+        <v>234</v>
       </c>
       <c r="D8">
-        <v>423128</v>
+        <v>381030</v>
       </c>
       <c r="E8">
-        <v>2073310</v>
+        <v>2314676</v>
       </c>
       <c r="F8">
-        <v>346069</v>
+        <v>369604</v>
       </c>
       <c r="G8">
-        <v>125.7</v>
+        <v>195.6</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -634,31 +610,28 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>44804</v>
       </c>
       <c r="B9">
-        <v>118409</v>
+        <v>124226</v>
       </c>
       <c r="C9">
-        <v>60.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D9">
-        <v>494024</v>
+        <v>597332</v>
       </c>
       <c r="E9">
-        <v>2617570</v>
+        <v>2835816</v>
       </c>
       <c r="F9">
-        <v>520805</v>
+        <v>653297</v>
       </c>
       <c r="G9">
-        <v>199.6</v>
+        <v>193</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -666,31 +639,28 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>44834</v>
       </c>
       <c r="B10">
-        <v>120652</v>
+        <v>120786</v>
       </c>
       <c r="C10">
-        <v>153.1</v>
+        <v>207.4</v>
       </c>
       <c r="D10">
-        <v>1511608</v>
+        <v>1855565</v>
       </c>
       <c r="E10">
-        <v>992965</v>
+        <v>1053766</v>
       </c>
       <c r="F10">
-        <v>95802</v>
+        <v>313178</v>
       </c>
       <c r="G10">
-        <v>76.2</v>
+        <v>80.3</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -698,31 +668,28 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>44865</v>
       </c>
       <c r="B11">
-        <v>143992</v>
+        <v>129792</v>
       </c>
       <c r="C11">
-        <v>269.2</v>
+        <v>139.3</v>
       </c>
       <c r="D11">
-        <v>2699272</v>
+        <v>1962897</v>
       </c>
       <c r="E11">
-        <v>4597334</v>
+        <v>3901709</v>
       </c>
       <c r="F11">
-        <v>450878</v>
+        <v>262391</v>
       </c>
       <c r="G11">
-        <v>247.8</v>
+        <v>235.4</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -730,31 +697,28 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>44895</v>
       </c>
       <c r="B12">
-        <v>193198</v>
+        <v>175226</v>
       </c>
       <c r="C12">
-        <v>555.4</v>
+        <v>417.8</v>
       </c>
       <c r="D12">
-        <v>1471890</v>
+        <v>855868</v>
       </c>
       <c r="E12">
-        <v>4068380</v>
+        <v>3412778</v>
       </c>
       <c r="F12">
-        <v>879001</v>
+        <v>765860</v>
       </c>
       <c r="G12">
-        <v>65.2</v>
+        <v>48.2</v>
       </c>
       <c r="H12">
         <v>7.87</v>
@@ -762,31 +726,28 @@
       <c r="I12">
         <v>1</v>
       </c>
-      <c r="J12">
-        <v>-7.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>44926</v>
       </c>
       <c r="B13">
-        <v>160719</v>
+        <v>153148</v>
       </c>
       <c r="C13">
-        <v>516.6</v>
+        <v>377.4</v>
       </c>
       <c r="D13">
-        <v>1311519</v>
+        <v>1080944</v>
       </c>
       <c r="E13">
-        <v>3986434</v>
+        <v>4368524</v>
       </c>
       <c r="F13">
-        <v>758441</v>
+        <v>658860</v>
       </c>
       <c r="G13">
-        <v>478.1</v>
+        <v>413</v>
       </c>
       <c r="H13">
         <v>5.66</v>
@@ -794,31 +755,28 @@
       <c r="I13">
         <v>1</v>
       </c>
-      <c r="J13">
-        <v>-5.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>44957</v>
       </c>
       <c r="B14">
-        <v>148423</v>
+        <v>145951</v>
       </c>
       <c r="C14">
-        <v>195.6</v>
+        <v>175.1</v>
       </c>
       <c r="D14">
-        <v>880064</v>
+        <v>979213</v>
       </c>
       <c r="E14">
-        <v>3595024</v>
+        <v>3936399</v>
       </c>
       <c r="F14">
-        <v>597414</v>
+        <v>349968</v>
       </c>
       <c r="G14">
-        <v>341.9</v>
+        <v>222.2</v>
       </c>
       <c r="H14">
         <v>4.1</v>
@@ -826,31 +784,28 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>44985</v>
       </c>
       <c r="B15">
-        <v>158817</v>
+        <v>152668</v>
       </c>
       <c r="C15">
-        <v>147</v>
+        <v>84.2</v>
       </c>
       <c r="D15">
-        <v>1379419</v>
+        <v>1933320</v>
       </c>
       <c r="E15">
-        <v>3249127</v>
+        <v>3477116</v>
       </c>
       <c r="F15">
-        <v>604739</v>
+        <v>615516</v>
       </c>
       <c r="G15">
-        <v>136.7</v>
+        <v>75.2</v>
       </c>
       <c r="H15">
         <v>5.38</v>
@@ -858,31 +813,28 @@
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>45016</v>
       </c>
       <c r="B16">
-        <v>131049</v>
+        <v>122159</v>
       </c>
       <c r="C16">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="D16">
-        <v>1302935</v>
+        <v>957443</v>
       </c>
       <c r="E16">
-        <v>2905306</v>
+        <v>3403321</v>
       </c>
       <c r="F16">
-        <v>344313</v>
+        <v>277729</v>
       </c>
       <c r="G16">
-        <v>321.9</v>
+        <v>311.1</v>
       </c>
       <c r="H16">
         <v>1.8</v>
@@ -890,31 +842,28 @@
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>45046</v>
       </c>
       <c r="B17">
-        <v>117148</v>
+        <v>124700</v>
       </c>
       <c r="C17">
-        <v>54.1</v>
+        <v>59.1</v>
       </c>
       <c r="D17">
-        <v>2063288</v>
+        <v>3158678</v>
       </c>
       <c r="E17">
-        <v>2872477</v>
+        <v>4279862</v>
       </c>
       <c r="F17">
-        <v>375493</v>
+        <v>311699</v>
       </c>
       <c r="G17">
-        <v>301.6</v>
+        <v>297</v>
       </c>
       <c r="H17">
         <v>2.81</v>
@@ -922,31 +871,28 @@
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>45077</v>
       </c>
       <c r="B18">
-        <v>111208</v>
+        <v>125431</v>
       </c>
       <c r="C18">
-        <v>78.40000000000001</v>
+        <v>141.4</v>
       </c>
       <c r="D18">
-        <v>1108188</v>
+        <v>1313149</v>
       </c>
       <c r="E18">
-        <v>1022399</v>
+        <v>1451426</v>
       </c>
       <c r="F18">
-        <v>177484</v>
+        <v>570197</v>
       </c>
       <c r="G18">
-        <v>221.1</v>
+        <v>224.4</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -954,31 +900,28 @@
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>45107</v>
       </c>
       <c r="B19">
-        <v>119904</v>
+        <v>131499</v>
       </c>
       <c r="C19">
-        <v>178.5</v>
+        <v>363.6</v>
       </c>
       <c r="D19">
-        <v>1132385</v>
+        <v>1007760</v>
       </c>
       <c r="E19">
-        <v>2334517</v>
+        <v>2250986</v>
       </c>
       <c r="F19">
-        <v>353300</v>
+        <v>370705</v>
       </c>
       <c r="G19">
-        <v>68.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -986,31 +929,28 @@
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>45138</v>
       </c>
       <c r="B20">
-        <v>131491</v>
+        <v>144079</v>
       </c>
       <c r="C20">
-        <v>152.1</v>
+        <v>285.5</v>
       </c>
       <c r="D20">
-        <v>1019157</v>
+        <v>945332</v>
       </c>
       <c r="E20">
-        <v>3658942</v>
+        <v>5144472</v>
       </c>
       <c r="F20">
-        <v>491206</v>
+        <v>318497</v>
       </c>
       <c r="G20">
-        <v>41.1</v>
+        <v>50.1</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1018,31 +958,28 @@
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>45169</v>
       </c>
       <c r="B21">
-        <v>119054</v>
+        <v>141628</v>
       </c>
       <c r="C21">
-        <v>107</v>
+        <v>189.8</v>
       </c>
       <c r="D21">
-        <v>821357</v>
+        <v>1188913</v>
       </c>
       <c r="E21">
-        <v>2185897</v>
+        <v>3108908</v>
       </c>
       <c r="F21">
-        <v>159115</v>
+        <v>128897</v>
       </c>
       <c r="G21">
-        <v>103.3</v>
+        <v>73.3</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1050,31 +987,28 @@
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>45199</v>
       </c>
       <c r="B22">
-        <v>110679</v>
+        <v>116805</v>
       </c>
       <c r="C22">
-        <v>168.7</v>
+        <v>231</v>
       </c>
       <c r="D22">
-        <v>1780195</v>
+        <v>2161311</v>
       </c>
       <c r="E22">
-        <v>1468129</v>
+        <v>1861361</v>
       </c>
       <c r="F22">
-        <v>324656</v>
+        <v>1032222</v>
       </c>
       <c r="G22">
-        <v>291.3</v>
+        <v>531.2</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1082,31 +1016,28 @@
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>45230</v>
       </c>
       <c r="B23">
-        <v>160950</v>
+        <v>147542</v>
       </c>
       <c r="C23">
-        <v>670.6</v>
+        <v>630.7</v>
       </c>
       <c r="D23">
-        <v>1949896</v>
+        <v>1478716</v>
       </c>
       <c r="E23">
-        <v>3730717</v>
+        <v>3092632</v>
       </c>
       <c r="F23">
-        <v>423351</v>
+        <v>348166</v>
       </c>
       <c r="G23">
-        <v>153.4</v>
+        <v>154.8</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1114,31 +1045,28 @@
       <c r="I23">
         <v>0</v>
       </c>
-      <c r="J23">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>45260</v>
       </c>
       <c r="B24">
-        <v>161947</v>
+        <v>146949</v>
       </c>
       <c r="C24">
-        <v>319</v>
+        <v>162.1</v>
       </c>
       <c r="D24">
-        <v>1548362</v>
+        <v>1137114</v>
       </c>
       <c r="E24">
-        <v>3049060</v>
+        <v>2605187</v>
       </c>
       <c r="F24">
-        <v>239888</v>
+        <v>153608</v>
       </c>
       <c r="G24">
-        <v>208.3</v>
+        <v>150</v>
       </c>
       <c r="H24">
         <v>1.46</v>
@@ -1146,31 +1074,28 @@
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>45291</v>
       </c>
       <c r="B25">
-        <v>156849</v>
+        <v>144622</v>
       </c>
       <c r="C25">
-        <v>534.5</v>
+        <v>385.8</v>
       </c>
       <c r="D25">
-        <v>1739544</v>
+        <v>843295</v>
       </c>
       <c r="E25">
-        <v>1771876</v>
+        <v>1158563</v>
       </c>
       <c r="F25">
-        <v>230752</v>
+        <v>228858</v>
       </c>
       <c r="G25">
-        <v>217.8</v>
+        <v>181.6</v>
       </c>
       <c r="H25">
         <v>1.52</v>
@@ -1178,31 +1103,28 @@
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="J25">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>45322</v>
       </c>
       <c r="B26">
-        <v>147211</v>
+        <v>147517</v>
       </c>
       <c r="C26">
-        <v>427</v>
+        <v>367.7</v>
       </c>
       <c r="D26">
-        <v>1679083</v>
+        <v>1738565</v>
       </c>
       <c r="E26">
-        <v>2599695</v>
+        <v>2352532</v>
       </c>
       <c r="F26">
-        <v>361269</v>
+        <v>364238</v>
       </c>
       <c r="G26">
-        <v>252.2</v>
+        <v>153.4</v>
       </c>
       <c r="H26">
         <v>7.47</v>
@@ -1210,31 +1132,28 @@
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26">
-        <v>-7.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>45351</v>
       </c>
       <c r="B27">
-        <v>135390</v>
+        <v>136523</v>
       </c>
       <c r="C27">
-        <v>95.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D27">
-        <v>1057330</v>
+        <v>428075</v>
       </c>
       <c r="E27">
-        <v>1421540</v>
+        <v>981375</v>
       </c>
       <c r="F27">
-        <v>219134</v>
+        <v>461027</v>
       </c>
       <c r="G27">
-        <v>313</v>
+        <v>272.6</v>
       </c>
       <c r="H27">
         <v>5.52</v>
@@ -1242,31 +1161,28 @@
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>45382</v>
       </c>
       <c r="B28">
-        <v>141286</v>
+        <v>128531</v>
       </c>
       <c r="C28">
-        <v>141.3</v>
+        <v>126.5</v>
       </c>
       <c r="D28">
-        <v>1113717</v>
+        <v>954517</v>
       </c>
       <c r="E28">
-        <v>4366543</v>
+        <v>5346107</v>
       </c>
       <c r="F28">
-        <v>686935</v>
+        <v>360918</v>
       </c>
       <c r="G28">
-        <v>296.8</v>
+        <v>251.7</v>
       </c>
       <c r="H28">
         <v>3.45</v>
@@ -1274,31 +1190,28 @@
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>45412</v>
       </c>
       <c r="B29">
-        <v>135773</v>
+        <v>136656</v>
       </c>
       <c r="C29">
-        <v>196.5</v>
+        <v>218.4</v>
       </c>
       <c r="D29">
-        <v>1682538</v>
+        <v>1971627</v>
       </c>
       <c r="E29">
-        <v>2253394</v>
+        <v>2272565</v>
       </c>
       <c r="F29">
-        <v>192392</v>
+        <v>181883</v>
       </c>
       <c r="G29">
-        <v>53.5</v>
+        <v>62.4</v>
       </c>
       <c r="H29">
         <v>4.84</v>
@@ -1306,31 +1219,28 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>45443</v>
       </c>
       <c r="B30">
-        <v>117451</v>
+        <v>113428</v>
       </c>
       <c r="C30">
-        <v>46.2</v>
+        <v>62.8</v>
       </c>
       <c r="D30">
-        <v>684058</v>
+        <v>441492</v>
       </c>
       <c r="E30">
-        <v>2599829</v>
+        <v>2617632</v>
       </c>
       <c r="F30">
-        <v>502657</v>
+        <v>605259</v>
       </c>
       <c r="G30">
-        <v>175.7</v>
+        <v>306.5</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1338,31 +1248,28 @@
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>45473</v>
       </c>
       <c r="B31">
-        <v>123071</v>
+        <v>134741</v>
       </c>
       <c r="C31">
-        <v>89.59999999999999</v>
+        <v>179.1</v>
       </c>
       <c r="D31">
-        <v>1090089</v>
+        <v>1873682</v>
       </c>
       <c r="E31">
-        <v>1229842</v>
+        <v>1542583</v>
       </c>
       <c r="F31">
-        <v>209692</v>
+        <v>514760</v>
       </c>
       <c r="G31">
-        <v>37</v>
+        <v>33.9</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -1370,31 +1277,28 @@
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>45504</v>
       </c>
       <c r="B32">
-        <v>115910</v>
+        <v>123774</v>
       </c>
       <c r="C32">
-        <v>50.4</v>
+        <v>22.2</v>
       </c>
       <c r="D32">
-        <v>1527847</v>
+        <v>2319502</v>
       </c>
       <c r="E32">
-        <v>1113806</v>
+        <v>1335833</v>
       </c>
       <c r="F32">
-        <v>123187</v>
+        <v>304542</v>
       </c>
       <c r="G32">
-        <v>109.2</v>
+        <v>128.3</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1402,31 +1306,28 @@
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>45535</v>
       </c>
       <c r="B33">
-        <v>120001</v>
+        <v>126502</v>
       </c>
       <c r="C33">
-        <v>102.5</v>
+        <v>164.8</v>
       </c>
       <c r="D33">
-        <v>1224888</v>
+        <v>1109885</v>
       </c>
       <c r="E33">
-        <v>2908325</v>
+        <v>3155182</v>
       </c>
       <c r="F33">
-        <v>470459</v>
+        <v>545782</v>
       </c>
       <c r="G33">
-        <v>76.2</v>
+        <v>118.2</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -1434,31 +1335,28 @@
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>45565</v>
       </c>
       <c r="B34">
-        <v>128831</v>
+        <v>133926</v>
       </c>
       <c r="C34">
-        <v>82.2</v>
+        <v>123.4</v>
       </c>
       <c r="D34">
-        <v>1294301</v>
+        <v>1531840</v>
       </c>
       <c r="E34">
-        <v>2320062</v>
+        <v>2807525</v>
       </c>
       <c r="F34">
-        <v>383960</v>
+        <v>425066</v>
       </c>
       <c r="G34">
-        <v>55.6</v>
+        <v>67.7</v>
       </c>
       <c r="H34">
         <v>0.27</v>
@@ -1466,31 +1364,28 @@
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="J34">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>45596</v>
       </c>
       <c r="B35">
-        <v>139353</v>
+        <v>113460</v>
       </c>
       <c r="C35">
-        <v>319.4</v>
+        <v>228.9</v>
       </c>
       <c r="D35">
-        <v>1483515</v>
+        <v>1082395</v>
       </c>
       <c r="E35">
-        <v>4053623</v>
+        <v>3016475</v>
       </c>
       <c r="F35">
-        <v>468576</v>
+        <v>310076</v>
       </c>
       <c r="G35">
-        <v>255.1</v>
+        <v>330.3</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -1498,31 +1393,28 @@
       <c r="I35">
         <v>0</v>
       </c>
-      <c r="J35">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>45626</v>
       </c>
       <c r="B36">
-        <v>153936</v>
+        <v>148296</v>
       </c>
       <c r="C36">
-        <v>380</v>
+        <v>289</v>
       </c>
       <c r="D36">
-        <v>760244</v>
+        <v>486351</v>
       </c>
       <c r="E36">
-        <v>1771499</v>
+        <v>1551924</v>
       </c>
       <c r="F36">
-        <v>297858</v>
+        <v>525542</v>
       </c>
       <c r="G36">
-        <v>165</v>
+        <v>119.5</v>
       </c>
       <c r="H36">
         <v>4.88</v>
@@ -1530,31 +1422,28 @@
       <c r="I36">
         <v>1</v>
       </c>
-      <c r="J36">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>45657</v>
       </c>
       <c r="B37">
-        <v>145630</v>
+        <v>139222</v>
       </c>
       <c r="C37">
-        <v>152.7</v>
+        <v>85.5</v>
       </c>
       <c r="D37">
-        <v>709670</v>
+        <v>520855</v>
       </c>
       <c r="E37">
-        <v>2217460</v>
+        <v>1813934</v>
       </c>
       <c r="F37">
-        <v>354328</v>
+        <v>422743</v>
       </c>
       <c r="G37">
-        <v>185.7</v>
+        <v>154.5</v>
       </c>
       <c r="H37">
         <v>6.36</v>
@@ -1562,31 +1451,28 @@
       <c r="I37">
         <v>1</v>
       </c>
-      <c r="J37">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>45688</v>
       </c>
       <c r="B38">
-        <v>143518</v>
+        <v>144283</v>
       </c>
       <c r="C38">
-        <v>188.6</v>
+        <v>141</v>
       </c>
       <c r="D38">
-        <v>878451</v>
+        <v>887866</v>
       </c>
       <c r="E38">
-        <v>4270052</v>
+        <v>4459717</v>
       </c>
       <c r="F38">
-        <v>905461</v>
+        <v>840026</v>
       </c>
       <c r="G38">
-        <v>295.3</v>
+        <v>230.8</v>
       </c>
       <c r="H38">
         <v>7.42</v>
@@ -1594,31 +1480,28 @@
       <c r="I38">
         <v>0</v>
       </c>
-      <c r="J38">
-        <v>-7.4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>45716</v>
       </c>
       <c r="B39">
-        <v>137056</v>
+        <v>138127</v>
       </c>
       <c r="C39">
-        <v>235.3</v>
+        <v>173.4</v>
       </c>
       <c r="D39">
-        <v>375084</v>
+        <v>400167</v>
       </c>
       <c r="E39">
-        <v>1453113</v>
+        <v>1246117</v>
       </c>
       <c r="F39">
-        <v>211914</v>
+        <v>463600</v>
       </c>
       <c r="G39">
-        <v>191.6</v>
+        <v>174.2</v>
       </c>
       <c r="H39">
         <v>11.8</v>
@@ -1626,31 +1509,28 @@
       <c r="I39">
         <v>0</v>
       </c>
-      <c r="J39">
-        <v>-11.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>45747</v>
       </c>
       <c r="B40">
-        <v>133194</v>
+        <v>131931</v>
       </c>
       <c r="C40">
-        <v>217.2</v>
+        <v>207.1</v>
       </c>
       <c r="D40">
-        <v>1980056</v>
+        <v>2347445</v>
       </c>
       <c r="E40">
-        <v>2730560</v>
+        <v>2302990</v>
       </c>
       <c r="F40">
-        <v>376919</v>
+        <v>305218</v>
       </c>
       <c r="G40">
-        <v>99.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H40">
         <v>0.6899999999999999</v>
@@ -1658,31 +1538,28 @@
       <c r="I40">
         <v>0</v>
       </c>
-      <c r="J40">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>45777</v>
       </c>
       <c r="B41">
-        <v>126784</v>
+        <v>126797</v>
       </c>
       <c r="C41">
-        <v>120.2</v>
+        <v>111.7</v>
       </c>
       <c r="D41">
-        <v>629721</v>
+        <v>717476</v>
       </c>
       <c r="E41">
-        <v>1823378</v>
+        <v>2122740</v>
       </c>
       <c r="F41">
-        <v>235768</v>
+        <v>283930</v>
       </c>
       <c r="G41">
-        <v>88.7</v>
+        <v>93</v>
       </c>
       <c r="H41">
         <v>3.79</v>
@@ -1690,31 +1567,28 @@
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>45808</v>
       </c>
       <c r="B42">
-        <v>120659</v>
+        <v>121718</v>
       </c>
       <c r="C42">
-        <v>60.7</v>
+        <v>27.3</v>
       </c>
       <c r="D42">
-        <v>443882</v>
+        <v>586282</v>
       </c>
       <c r="E42">
-        <v>1411393</v>
+        <v>1085472</v>
       </c>
       <c r="F42">
-        <v>157191</v>
+        <v>195272</v>
       </c>
       <c r="G42">
-        <v>55.8</v>
+        <v>81</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -1722,31 +1596,28 @@
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>45838</v>
       </c>
       <c r="B43">
-        <v>108578</v>
+        <v>110524</v>
       </c>
       <c r="C43">
-        <v>50.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D43">
-        <v>856377</v>
+        <v>1135371</v>
       </c>
       <c r="E43">
-        <v>1151445</v>
+        <v>1661983</v>
       </c>
       <c r="F43">
-        <v>111886</v>
+        <v>225267</v>
       </c>
       <c r="G43">
-        <v>232.5</v>
+        <v>256.6</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -1754,31 +1625,28 @@
       <c r="I43">
         <v>0</v>
       </c>
-      <c r="J43">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>45869</v>
       </c>
       <c r="B44">
-        <v>114893</v>
+        <v>119213</v>
       </c>
       <c r="C44">
-        <v>134.7</v>
+        <v>294.6</v>
       </c>
       <c r="D44">
-        <v>1101546</v>
+        <v>1613095</v>
       </c>
       <c r="E44">
-        <v>2553791</v>
+        <v>2918526</v>
       </c>
       <c r="F44">
-        <v>300954</v>
+        <v>258338</v>
       </c>
       <c r="G44">
-        <v>123</v>
+        <v>113.5</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -1786,31 +1654,28 @@
       <c r="I44">
         <v>0</v>
       </c>
-      <c r="J44">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>45900</v>
       </c>
       <c r="B45">
-        <v>114976</v>
+        <v>118613</v>
       </c>
       <c r="C45">
-        <v>42</v>
+        <v>61.7</v>
       </c>
       <c r="D45">
-        <v>310419</v>
+        <v>443048</v>
       </c>
       <c r="E45">
-        <v>1216394</v>
+        <v>1896755</v>
       </c>
       <c r="F45">
-        <v>137087</v>
+        <v>237670</v>
       </c>
       <c r="G45">
-        <v>126.9</v>
+        <v>120.8</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -1818,31 +1683,28 @@
       <c r="I45">
         <v>0</v>
       </c>
-      <c r="J45">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>45930</v>
       </c>
       <c r="B46">
-        <v>113009</v>
+        <v>103683</v>
       </c>
       <c r="C46">
-        <v>132</v>
+        <v>90.3</v>
       </c>
       <c r="D46">
-        <v>410257</v>
+        <v>313368</v>
       </c>
       <c r="E46">
-        <v>2078090</v>
+        <v>2613845</v>
       </c>
       <c r="F46">
-        <v>172342</v>
+        <v>153274</v>
       </c>
       <c r="G46">
-        <v>171.5</v>
+        <v>310.7</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -1850,31 +1712,28 @@
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45961</v>
       </c>
       <c r="B47">
-        <v>131556</v>
+        <v>110088</v>
       </c>
       <c r="C47">
-        <v>136.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D47">
-        <v>2407522</v>
+        <v>1335610</v>
       </c>
       <c r="E47">
-        <v>3354590</v>
+        <v>2792004</v>
       </c>
       <c r="F47">
-        <v>259057</v>
+        <v>186173</v>
       </c>
       <c r="G47">
-        <v>260.9</v>
+        <v>337.2</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -1882,31 +1741,28 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>45991</v>
       </c>
       <c r="B48">
-        <v>149487</v>
+        <v>136702</v>
       </c>
       <c r="C48">
-        <v>375.8</v>
+        <v>288.9</v>
       </c>
       <c r="D48">
-        <v>2086526</v>
+        <v>1742912</v>
       </c>
       <c r="E48">
-        <v>4785891</v>
+        <v>3607392</v>
       </c>
       <c r="F48">
-        <v>591303</v>
+        <v>266888</v>
       </c>
       <c r="G48">
-        <v>373.1</v>
+        <v>228.7</v>
       </c>
       <c r="H48">
         <v>4.06</v>
@@ -1914,40 +1770,34 @@
       <c r="I48">
         <v>1</v>
       </c>
-      <c r="J48">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>46022</v>
       </c>
       <c r="B49">
-        <v>191421</v>
+        <v>169710</v>
       </c>
       <c r="C49">
-        <v>461</v>
+        <v>296.5</v>
       </c>
       <c r="D49">
-        <v>2944557</v>
+        <v>2490256</v>
       </c>
       <c r="E49">
-        <v>4863987</v>
+        <v>4603399</v>
       </c>
       <c r="F49">
-        <v>643512</v>
+        <v>280892</v>
       </c>
       <c r="G49">
-        <v>146.3</v>
+        <v>104.1</v>
       </c>
       <c r="H49">
         <v>9.34</v>
       </c>
       <c r="I49">
         <v>1</v>
-      </c>
-      <c r="J49">
-        <v>-9.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/static/sample-data/synth_otc_pharma.xlsx
+++ b/static/sample-data/synth_otc_pharma.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>date</t>
   </si>
@@ -22,13 +22,25 @@
     <t>sales_packs</t>
   </si>
   <si>
+    <t>tv_spend</t>
+  </si>
+  <si>
     <t>tv_trp</t>
   </si>
   <si>
-    <t>apteka_ooh_contacts</t>
+    <t>apteka_spend</t>
+  </si>
+  <si>
+    <t>apteka_contacts</t>
   </si>
   <si>
     <t>digital_spend</t>
+  </si>
+  <si>
+    <t>digital_impressions</t>
+  </si>
+  <si>
+    <t>performance_spend</t>
   </si>
   <si>
     <t>performance_clicks</t>
@@ -40,7 +52,7 @@
     <t>weather_temp_low</t>
   </si>
   <si>
-    <t>holiday_newyear</t>
+    <t>category_sales</t>
   </si>
 </sst>
 </file>
@@ -376,10 +388,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -407,1397 +419,1985 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>44592</v>
       </c>
       <c r="B2">
-        <v>134278</v>
+        <v>1070757</v>
       </c>
       <c r="C2">
-        <v>257.2</v>
+        <v>22144623</v>
       </c>
       <c r="D2">
-        <v>2799296</v>
+        <v>127.1</v>
       </c>
       <c r="E2">
-        <v>2455759</v>
+        <v>3023063</v>
       </c>
       <c r="F2">
-        <v>113160</v>
+        <v>8051534</v>
       </c>
       <c r="G2">
-        <v>227.8</v>
+        <v>1651420</v>
       </c>
       <c r="H2">
-        <v>4.28</v>
+        <v>7882354</v>
       </c>
       <c r="I2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>3728343</v>
+      </c>
+      <c r="J2">
+        <v>106585</v>
+      </c>
+      <c r="K2">
+        <v>209.8</v>
+      </c>
+      <c r="L2">
+        <v>3.07</v>
+      </c>
+      <c r="M2">
+        <v>5016366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>44620</v>
       </c>
       <c r="B3">
-        <v>143809</v>
+        <v>1084946</v>
       </c>
       <c r="C3">
-        <v>58.4</v>
+        <v>7412222</v>
       </c>
       <c r="D3">
-        <v>808876</v>
+        <v>40.7</v>
       </c>
       <c r="E3">
-        <v>3528676</v>
+        <v>5691435</v>
       </c>
       <c r="F3">
-        <v>143241</v>
+        <v>14045969</v>
       </c>
       <c r="G3">
-        <v>63.5</v>
+        <v>1053042</v>
       </c>
       <c r="H3">
-        <v>6.05</v>
+        <v>5116459</v>
       </c>
       <c r="I3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>3110262</v>
+      </c>
+      <c r="J3">
+        <v>85710</v>
+      </c>
+      <c r="K3">
+        <v>150.3</v>
+      </c>
+      <c r="L3">
+        <v>7.54</v>
+      </c>
+      <c r="M3">
+        <v>4937246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>44651</v>
       </c>
       <c r="B4">
-        <v>122774</v>
+        <v>930908</v>
       </c>
       <c r="C4">
-        <v>54.4</v>
+        <v>7101389</v>
       </c>
       <c r="D4">
-        <v>2394175</v>
+        <v>39.4</v>
       </c>
       <c r="E4">
-        <v>914663</v>
+        <v>2921811</v>
       </c>
       <c r="F4">
-        <v>359245</v>
+        <v>7457821</v>
       </c>
       <c r="G4">
-        <v>300.3</v>
+        <v>27064</v>
       </c>
       <c r="H4">
-        <v>3.8</v>
+        <v>139028</v>
       </c>
       <c r="I4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>122542</v>
+      </c>
+      <c r="J4">
+        <v>3528</v>
+      </c>
+      <c r="K4">
+        <v>90.2</v>
+      </c>
+      <c r="L4">
+        <v>3.98</v>
+      </c>
+      <c r="M4">
+        <v>4533700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>44681</v>
       </c>
       <c r="B5">
-        <v>121297</v>
+        <v>984648</v>
       </c>
       <c r="C5">
-        <v>311.6</v>
+        <v>26740913</v>
       </c>
       <c r="D5">
-        <v>1068395</v>
+        <v>148.7</v>
       </c>
       <c r="E5">
-        <v>1074130</v>
+        <v>94837</v>
       </c>
       <c r="F5">
-        <v>489336</v>
+        <v>236555</v>
       </c>
       <c r="G5">
-        <v>193.9</v>
+        <v>2793323</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>13988333</v>
       </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>7177972</v>
+      </c>
+      <c r="J5">
+        <v>198586</v>
+      </c>
+      <c r="K5">
+        <v>481.5</v>
+      </c>
+      <c r="L5">
+        <v>4.78</v>
+      </c>
+      <c r="M5">
+        <v>4147856</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>44712</v>
       </c>
       <c r="B6">
-        <v>108488</v>
+        <v>943398</v>
       </c>
       <c r="C6">
-        <v>163.7</v>
+        <v>15098334</v>
       </c>
       <c r="D6">
-        <v>581067</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="E6">
-        <v>4117782</v>
+        <v>50156</v>
       </c>
       <c r="F6">
-        <v>142338</v>
+        <v>126757</v>
       </c>
       <c r="G6">
-        <v>380.7</v>
+        <v>3759287</v>
       </c>
       <c r="H6">
+        <v>18293049</v>
+      </c>
+      <c r="I6">
+        <v>5681701</v>
+      </c>
+      <c r="J6">
+        <v>170047</v>
+      </c>
+      <c r="K6">
+        <v>124.2</v>
+      </c>
+      <c r="L6">
         <v>0</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="M6">
+        <v>3704275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>44742</v>
       </c>
       <c r="B7">
-        <v>121199</v>
+        <v>807316</v>
       </c>
       <c r="C7">
-        <v>125.4</v>
+        <v>12796587</v>
       </c>
       <c r="D7">
-        <v>1151655</v>
+        <v>73</v>
       </c>
       <c r="E7">
-        <v>2163899</v>
+        <v>39127</v>
       </c>
       <c r="F7">
-        <v>301538</v>
+        <v>98886</v>
       </c>
       <c r="G7">
-        <v>99.40000000000001</v>
+        <v>928709</v>
       </c>
       <c r="H7">
+        <v>4719228</v>
+      </c>
+      <c r="I7">
+        <v>2312561</v>
+      </c>
+      <c r="J7">
+        <v>69992</v>
+      </c>
+      <c r="K7">
+        <v>171.3</v>
+      </c>
+      <c r="L7">
         <v>0</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="M7">
+        <v>3624774</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>44773</v>
       </c>
       <c r="B8">
-        <v>111728</v>
+        <v>862777</v>
       </c>
       <c r="C8">
-        <v>234</v>
+        <v>19787059</v>
       </c>
       <c r="D8">
-        <v>381030</v>
+        <v>113.3</v>
       </c>
       <c r="E8">
-        <v>2314676</v>
+        <v>918590</v>
       </c>
       <c r="F8">
-        <v>369604</v>
+        <v>2319774</v>
       </c>
       <c r="G8">
-        <v>195.6</v>
+        <v>2430470</v>
       </c>
       <c r="H8">
+        <v>11847177</v>
+      </c>
+      <c r="I8">
+        <v>4559676</v>
+      </c>
+      <c r="J8">
+        <v>125033</v>
+      </c>
+      <c r="K8">
+        <v>95.8</v>
+      </c>
+      <c r="L8">
         <v>0</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="M8">
+        <v>3209504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>44804</v>
       </c>
       <c r="B9">
-        <v>124226</v>
+        <v>872523</v>
       </c>
       <c r="C9">
-        <v>79.09999999999999</v>
+        <v>7526403</v>
       </c>
       <c r="D9">
-        <v>597332</v>
+        <v>45</v>
       </c>
       <c r="E9">
-        <v>2835816</v>
+        <v>3473118</v>
       </c>
       <c r="F9">
-        <v>653297</v>
+        <v>8714548</v>
       </c>
       <c r="G9">
-        <v>193</v>
+        <v>2658345</v>
       </c>
       <c r="H9">
+        <v>12425365</v>
+      </c>
+      <c r="I9">
+        <v>8799150</v>
+      </c>
+      <c r="J9">
+        <v>250664</v>
+      </c>
+      <c r="K9">
+        <v>233.5</v>
+      </c>
+      <c r="L9">
         <v>0</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="M9">
+        <v>3550196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>44834</v>
       </c>
       <c r="B10">
-        <v>120786</v>
+        <v>1040679</v>
       </c>
       <c r="C10">
-        <v>207.4</v>
+        <v>20322062</v>
       </c>
       <c r="D10">
-        <v>1855565</v>
+        <v>109.5</v>
       </c>
       <c r="E10">
-        <v>1053766</v>
+        <v>3400779</v>
       </c>
       <c r="F10">
-        <v>313178</v>
+        <v>8347790</v>
       </c>
       <c r="G10">
-        <v>80.3</v>
+        <v>5420406</v>
       </c>
       <c r="H10">
+        <v>24738260</v>
+      </c>
+      <c r="I10">
+        <v>7109365</v>
+      </c>
+      <c r="J10">
+        <v>194130</v>
+      </c>
+      <c r="K10">
+        <v>37.2</v>
+      </c>
+      <c r="L10">
         <v>0</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="M10">
+        <v>3964533</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>44865</v>
       </c>
       <c r="B11">
-        <v>129792</v>
+        <v>1134122</v>
       </c>
       <c r="C11">
-        <v>139.3</v>
+        <v>13577245</v>
       </c>
       <c r="D11">
-        <v>1962897</v>
+        <v>72.7</v>
       </c>
       <c r="E11">
-        <v>3901709</v>
+        <v>5492891</v>
       </c>
       <c r="F11">
-        <v>262391</v>
+        <v>13521379</v>
       </c>
       <c r="G11">
-        <v>235.4</v>
+        <v>2595130</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>12248079</v>
       </c>
       <c r="I11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>12132939</v>
+      </c>
+      <c r="J11">
+        <v>349912</v>
+      </c>
+      <c r="K11">
+        <v>79.8</v>
+      </c>
+      <c r="L11">
+        <v>1.07</v>
+      </c>
+      <c r="M11">
+        <v>4220852</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>44895</v>
       </c>
       <c r="B12">
-        <v>175226</v>
+        <v>1231771</v>
       </c>
       <c r="C12">
-        <v>417.8</v>
+        <v>36694546</v>
       </c>
       <c r="D12">
-        <v>855868</v>
+        <v>196.1</v>
       </c>
       <c r="E12">
-        <v>3412778</v>
+        <v>1665030</v>
       </c>
       <c r="F12">
-        <v>765860</v>
+        <v>3881790</v>
       </c>
       <c r="G12">
-        <v>48.2</v>
+        <v>1722759</v>
       </c>
       <c r="H12">
-        <v>7.87</v>
+        <v>8495225</v>
       </c>
       <c r="I12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>6330409</v>
+      </c>
+      <c r="J12">
+        <v>178841</v>
+      </c>
+      <c r="K12">
+        <v>118.5</v>
+      </c>
+      <c r="L12">
+        <v>4.27</v>
+      </c>
+      <c r="M12">
+        <v>4310613</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>44926</v>
       </c>
       <c r="B13">
-        <v>153148</v>
+        <v>1222747</v>
       </c>
       <c r="C13">
-        <v>377.4</v>
+        <v>33036147</v>
       </c>
       <c r="D13">
-        <v>1080944</v>
+        <v>178.7</v>
       </c>
       <c r="E13">
-        <v>4368524</v>
+        <v>4659486</v>
       </c>
       <c r="F13">
-        <v>658860</v>
+        <v>11001140</v>
       </c>
       <c r="G13">
-        <v>413</v>
+        <v>126219</v>
       </c>
       <c r="H13">
-        <v>5.66</v>
+        <v>586071</v>
       </c>
       <c r="I13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>3514642</v>
+      </c>
+      <c r="J13">
+        <v>92768</v>
+      </c>
+      <c r="K13">
+        <v>272.3</v>
+      </c>
+      <c r="L13">
+        <v>1.91</v>
+      </c>
+      <c r="M13">
+        <v>4899182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>44957</v>
       </c>
       <c r="B14">
-        <v>145951</v>
+        <v>1302619</v>
       </c>
       <c r="C14">
-        <v>175.1</v>
+        <v>19219707</v>
       </c>
       <c r="D14">
-        <v>979213</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E14">
-        <v>3936399</v>
+        <v>6681870</v>
       </c>
       <c r="F14">
-        <v>349968</v>
+        <v>15672879</v>
       </c>
       <c r="G14">
-        <v>222.2</v>
+        <v>5187574</v>
       </c>
       <c r="H14">
-        <v>4.1</v>
+        <v>25639471</v>
       </c>
       <c r="I14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>3189373</v>
+      </c>
+      <c r="J14">
+        <v>86941</v>
+      </c>
+      <c r="K14">
+        <v>197.6</v>
+      </c>
+      <c r="L14">
+        <v>5.65</v>
+      </c>
+      <c r="M14">
+        <v>5193009</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>44985</v>
       </c>
       <c r="B15">
-        <v>152668</v>
+        <v>1352702</v>
       </c>
       <c r="C15">
-        <v>84.2</v>
+        <v>8800646</v>
       </c>
       <c r="D15">
-        <v>1933320</v>
+        <v>47.5</v>
       </c>
       <c r="E15">
-        <v>3477116</v>
+        <v>8294334</v>
       </c>
       <c r="F15">
-        <v>615516</v>
+        <v>18943476</v>
       </c>
       <c r="G15">
-        <v>75.2</v>
+        <v>2388633</v>
       </c>
       <c r="H15">
-        <v>5.38</v>
+        <v>11495902</v>
       </c>
       <c r="I15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>8733175</v>
+      </c>
+      <c r="J15">
+        <v>232327</v>
+      </c>
+      <c r="K15">
+        <v>52.1</v>
+      </c>
+      <c r="L15">
+        <v>12.63</v>
+      </c>
+      <c r="M15">
+        <v>4992821</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>45016</v>
       </c>
       <c r="B16">
-        <v>122159</v>
+        <v>1140319</v>
       </c>
       <c r="C16">
-        <v>135</v>
+        <v>14290541</v>
       </c>
       <c r="D16">
-        <v>957443</v>
+        <v>71.2</v>
       </c>
       <c r="E16">
-        <v>3403321</v>
+        <v>186180</v>
       </c>
       <c r="F16">
-        <v>277729</v>
+        <v>447503</v>
       </c>
       <c r="G16">
-        <v>311.1</v>
+        <v>4910977</v>
       </c>
       <c r="H16">
-        <v>1.8</v>
+        <v>23682961</v>
       </c>
       <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>3353874</v>
+      </c>
+      <c r="J16">
+        <v>90515</v>
+      </c>
+      <c r="K16">
+        <v>178.4</v>
+      </c>
+      <c r="L16">
+        <v>5.26</v>
+      </c>
+      <c r="M16">
+        <v>4461682</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>45046</v>
       </c>
       <c r="B17">
-        <v>124700</v>
+        <v>1024015</v>
       </c>
       <c r="C17">
-        <v>59.1</v>
+        <v>8343761</v>
       </c>
       <c r="D17">
-        <v>3158678</v>
+        <v>44</v>
       </c>
       <c r="E17">
-        <v>4279862</v>
+        <v>4189584</v>
       </c>
       <c r="F17">
-        <v>311699</v>
+        <v>9741302</v>
       </c>
       <c r="G17">
-        <v>297</v>
+        <v>2248621</v>
       </c>
       <c r="H17">
-        <v>2.81</v>
+        <v>10652534</v>
       </c>
       <c r="I17">
+        <v>3470816</v>
+      </c>
+      <c r="J17">
+        <v>90194</v>
+      </c>
+      <c r="K17">
+        <v>110.4</v>
+      </c>
+      <c r="L17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="M17">
+        <v>4662684</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>45077</v>
       </c>
       <c r="B18">
-        <v>125431</v>
+        <v>882956</v>
       </c>
       <c r="C18">
-        <v>141.4</v>
+        <v>14672483</v>
       </c>
       <c r="D18">
-        <v>1313149</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E18">
-        <v>1451426</v>
+        <v>2949944</v>
       </c>
       <c r="F18">
-        <v>570197</v>
+        <v>7035862</v>
       </c>
       <c r="G18">
-        <v>224.4</v>
+        <v>2500488</v>
       </c>
       <c r="H18">
+        <v>11604860</v>
+      </c>
+      <c r="I18">
+        <v>110181</v>
+      </c>
+      <c r="J18">
+        <v>3003</v>
+      </c>
+      <c r="K18">
+        <v>59.7</v>
+      </c>
+      <c r="L18">
         <v>0</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="M18">
+        <v>4023385</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>45107</v>
       </c>
       <c r="B19">
-        <v>131499</v>
+        <v>807146</v>
       </c>
       <c r="C19">
-        <v>363.6</v>
+        <v>31849316</v>
       </c>
       <c r="D19">
-        <v>1007760</v>
+        <v>170.7</v>
       </c>
       <c r="E19">
-        <v>2250986</v>
+        <v>1991623</v>
       </c>
       <c r="F19">
-        <v>370705</v>
+        <v>4874196</v>
       </c>
       <c r="G19">
-        <v>66.09999999999999</v>
+        <v>4820713</v>
       </c>
       <c r="H19">
+        <v>22241423</v>
+      </c>
+      <c r="I19">
+        <v>141082</v>
+      </c>
+      <c r="J19">
+        <v>4129</v>
+      </c>
+      <c r="K19">
+        <v>268.9</v>
+      </c>
+      <c r="L19">
         <v>0</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="M19">
+        <v>3613825</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>45138</v>
       </c>
       <c r="B20">
-        <v>144079</v>
+        <v>970592</v>
       </c>
       <c r="C20">
-        <v>285.5</v>
+        <v>25770351</v>
       </c>
       <c r="D20">
-        <v>945332</v>
+        <v>136.3</v>
       </c>
       <c r="E20">
-        <v>5144472</v>
+        <v>7612168</v>
       </c>
       <c r="F20">
-        <v>318497</v>
+        <v>17400154</v>
       </c>
       <c r="G20">
-        <v>50.1</v>
+        <v>2841162</v>
       </c>
       <c r="H20">
+        <v>13354598</v>
+      </c>
+      <c r="I20">
+        <v>4723498</v>
+      </c>
+      <c r="J20">
+        <v>131977</v>
+      </c>
+      <c r="K20">
+        <v>110.6</v>
+      </c>
+      <c r="L20">
         <v>0</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="M20">
+        <v>3877300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>45169</v>
       </c>
       <c r="B21">
-        <v>141628</v>
+        <v>881269</v>
       </c>
       <c r="C21">
-        <v>189.8</v>
+        <v>18580948</v>
       </c>
       <c r="D21">
-        <v>1188913</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E21">
-        <v>3108908</v>
+        <v>2617931</v>
       </c>
       <c r="F21">
-        <v>128897</v>
+        <v>6359816</v>
       </c>
       <c r="G21">
-        <v>73.3</v>
+        <v>47168</v>
       </c>
       <c r="H21">
+        <v>234501</v>
+      </c>
+      <c r="I21">
+        <v>3458430</v>
+      </c>
+      <c r="J21">
+        <v>91953</v>
+      </c>
+      <c r="K21">
+        <v>217.2</v>
+      </c>
+      <c r="L21">
         <v>0</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="M21">
+        <v>3561377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>45199</v>
       </c>
       <c r="B22">
-        <v>116805</v>
+        <v>896282</v>
       </c>
       <c r="C22">
-        <v>231</v>
+        <v>24547142</v>
       </c>
       <c r="D22">
-        <v>2161311</v>
+        <v>119.2</v>
       </c>
       <c r="E22">
-        <v>1861361</v>
+        <v>110979</v>
       </c>
       <c r="F22">
-        <v>1032222</v>
+        <v>238660</v>
       </c>
       <c r="G22">
-        <v>531.2</v>
+        <v>1458080</v>
       </c>
       <c r="H22">
+        <v>6603759</v>
+      </c>
+      <c r="I22">
+        <v>4059103</v>
+      </c>
+      <c r="J22">
+        <v>106262</v>
+      </c>
+      <c r="K22">
+        <v>401.7</v>
+      </c>
+      <c r="L22">
         <v>0</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="M22">
+        <v>3668011</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>45230</v>
       </c>
       <c r="B23">
-        <v>147542</v>
+        <v>1196548</v>
       </c>
       <c r="C23">
-        <v>630.7</v>
+        <v>58229452</v>
       </c>
       <c r="D23">
-        <v>1478716</v>
+        <v>296.4</v>
       </c>
       <c r="E23">
-        <v>3092632</v>
+        <v>2568462</v>
       </c>
       <c r="F23">
-        <v>348166</v>
+        <v>5517293</v>
       </c>
       <c r="G23">
-        <v>154.8</v>
+        <v>7130111</v>
       </c>
       <c r="H23">
+        <v>31998692</v>
+      </c>
+      <c r="I23">
+        <v>11047663</v>
+      </c>
+      <c r="J23">
+        <v>292743</v>
+      </c>
+      <c r="K23">
+        <v>195.4</v>
+      </c>
+      <c r="L23">
         <v>0</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="M23">
+        <v>4284966</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>45260</v>
       </c>
       <c r="B24">
-        <v>146949</v>
+        <v>1223240</v>
       </c>
       <c r="C24">
-        <v>162.1</v>
+        <v>16285607</v>
       </c>
       <c r="D24">
-        <v>1137114</v>
+        <v>81.2</v>
       </c>
       <c r="E24">
-        <v>2605187</v>
+        <v>1219324</v>
       </c>
       <c r="F24">
-        <v>153608</v>
+        <v>2989570</v>
       </c>
       <c r="G24">
-        <v>150</v>
+        <v>2496139</v>
       </c>
       <c r="H24">
-        <v>1.46</v>
+        <v>11147586</v>
       </c>
       <c r="I24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>2870936</v>
+      </c>
+      <c r="J24">
+        <v>72594</v>
+      </c>
+      <c r="K24">
+        <v>106.9</v>
+      </c>
+      <c r="L24">
+        <v>5.45</v>
+      </c>
+      <c r="M24">
+        <v>4737504</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>45291</v>
       </c>
       <c r="B25">
-        <v>144622</v>
+        <v>1302099</v>
       </c>
       <c r="C25">
-        <v>385.8</v>
+        <v>36741453</v>
       </c>
       <c r="D25">
-        <v>843295</v>
+        <v>181.4</v>
       </c>
       <c r="E25">
-        <v>1158563</v>
+        <v>80799</v>
       </c>
       <c r="F25">
-        <v>228858</v>
+        <v>179588</v>
       </c>
       <c r="G25">
-        <v>181.6</v>
+        <v>1589706</v>
       </c>
       <c r="H25">
-        <v>1.52</v>
+        <v>7400681</v>
       </c>
       <c r="I25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>8589157</v>
+      </c>
+      <c r="J25">
+        <v>228215</v>
+      </c>
+      <c r="K25">
+        <v>151.4</v>
+      </c>
+      <c r="L25">
+        <v>4.15</v>
+      </c>
+      <c r="M25">
+        <v>4712082</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>45322</v>
       </c>
       <c r="B26">
-        <v>147517</v>
+        <v>1403636</v>
       </c>
       <c r="C26">
-        <v>367.7</v>
+        <v>34418940</v>
       </c>
       <c r="D26">
-        <v>1738565</v>
+        <v>171.7</v>
       </c>
       <c r="E26">
-        <v>2352532</v>
+        <v>54417</v>
       </c>
       <c r="F26">
-        <v>364238</v>
+        <v>127027</v>
       </c>
       <c r="G26">
-        <v>153.4</v>
+        <v>1599669</v>
       </c>
       <c r="H26">
-        <v>7.47</v>
+        <v>7306026</v>
       </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>8501056</v>
+      </c>
+      <c r="J26">
+        <v>228964</v>
+      </c>
+      <c r="K26">
+        <v>72.5</v>
+      </c>
+      <c r="L26">
+        <v>12.47</v>
+      </c>
+      <c r="M26">
+        <v>5287540</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>45351</v>
       </c>
       <c r="B27">
-        <v>136523</v>
+        <v>1170302</v>
       </c>
       <c r="C27">
-        <v>69.90000000000001</v>
+        <v>10388696</v>
       </c>
       <c r="D27">
-        <v>428075</v>
+        <v>49.4</v>
       </c>
       <c r="E27">
-        <v>981375</v>
+        <v>2398469</v>
       </c>
       <c r="F27">
-        <v>461027</v>
+        <v>5344893</v>
       </c>
       <c r="G27">
-        <v>272.6</v>
+        <v>3017606</v>
       </c>
       <c r="H27">
-        <v>5.52</v>
+        <v>13844390</v>
       </c>
       <c r="I27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>197563</v>
+      </c>
+      <c r="J27">
+        <v>4984</v>
+      </c>
+      <c r="K27">
+        <v>303.7</v>
+      </c>
+      <c r="L27">
+        <v>7.49</v>
+      </c>
+      <c r="M27">
+        <v>5243526</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>45382</v>
       </c>
       <c r="B28">
-        <v>128531</v>
+        <v>1206278</v>
       </c>
       <c r="C28">
-        <v>126.5</v>
+        <v>15886715</v>
       </c>
       <c r="D28">
-        <v>954517</v>
+        <v>80.5</v>
       </c>
       <c r="E28">
-        <v>5346107</v>
+        <v>6135648</v>
       </c>
       <c r="F28">
-        <v>360918</v>
+        <v>13775344</v>
       </c>
       <c r="G28">
-        <v>251.7</v>
+        <v>4076384</v>
       </c>
       <c r="H28">
+        <v>17914373</v>
+      </c>
+      <c r="I28">
+        <v>8877100</v>
+      </c>
+      <c r="J28">
+        <v>233849</v>
+      </c>
+      <c r="K28">
+        <v>170.4</v>
+      </c>
+      <c r="L28">
         <v>3.45</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="M28">
+        <v>4484401</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>45412</v>
       </c>
       <c r="B29">
-        <v>136656</v>
+        <v>1034758</v>
       </c>
       <c r="C29">
-        <v>218.4</v>
+        <v>20730794</v>
       </c>
       <c r="D29">
-        <v>1971627</v>
+        <v>105.6</v>
       </c>
       <c r="E29">
-        <v>2272565</v>
+        <v>3665787</v>
       </c>
       <c r="F29">
-        <v>181883</v>
+        <v>8926289</v>
       </c>
       <c r="G29">
-        <v>62.4</v>
+        <v>2627799</v>
       </c>
       <c r="H29">
-        <v>4.84</v>
+        <v>12508594</v>
       </c>
       <c r="I29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>5473182</v>
+      </c>
+      <c r="J29">
+        <v>139643</v>
+      </c>
+      <c r="K29">
+        <v>464.5</v>
+      </c>
+      <c r="L29">
+        <v>4.72</v>
+      </c>
+      <c r="M29">
+        <v>4241984</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>45443</v>
       </c>
       <c r="B30">
-        <v>113428</v>
+        <v>899792</v>
       </c>
       <c r="C30">
-        <v>62.8</v>
+        <v>7674393</v>
       </c>
       <c r="D30">
-        <v>441492</v>
+        <v>39.6</v>
       </c>
       <c r="E30">
-        <v>2617632</v>
+        <v>38697</v>
       </c>
       <c r="F30">
-        <v>605259</v>
+        <v>86432</v>
       </c>
       <c r="G30">
-        <v>306.5</v>
+        <v>36883</v>
       </c>
       <c r="H30">
+        <v>167484</v>
+      </c>
+      <c r="I30">
+        <v>3326099</v>
+      </c>
+      <c r="J30">
+        <v>89046</v>
+      </c>
+      <c r="K30">
+        <v>176.6</v>
+      </c>
+      <c r="L30">
         <v>0</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="M30">
+        <v>3760638</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>45473</v>
       </c>
       <c r="B31">
-        <v>134741</v>
+        <v>847066</v>
       </c>
       <c r="C31">
-        <v>179.1</v>
+        <v>19150850</v>
       </c>
       <c r="D31">
-        <v>1873682</v>
+        <v>97.7</v>
       </c>
       <c r="E31">
-        <v>1542583</v>
+        <v>4119922</v>
       </c>
       <c r="F31">
-        <v>514760</v>
+        <v>9027621</v>
       </c>
       <c r="G31">
-        <v>33.9</v>
+        <v>5183506</v>
       </c>
       <c r="H31">
+        <v>22669850</v>
+      </c>
+      <c r="I31">
+        <v>2024986</v>
+      </c>
+      <c r="J31">
+        <v>55181</v>
+      </c>
+      <c r="K31">
+        <v>192.8</v>
+      </c>
+      <c r="L31">
         <v>0</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="M31">
+        <v>3470538</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
         <v>45504</v>
       </c>
       <c r="B32">
-        <v>123774</v>
+        <v>722797</v>
       </c>
       <c r="C32">
-        <v>22.2</v>
+        <v>2296537</v>
       </c>
       <c r="D32">
-        <v>2319502</v>
+        <v>12.4</v>
       </c>
       <c r="E32">
-        <v>1335833</v>
+        <v>556981</v>
       </c>
       <c r="F32">
-        <v>304542</v>
+        <v>1254641</v>
       </c>
       <c r="G32">
-        <v>128.3</v>
+        <v>85009</v>
       </c>
       <c r="H32">
+        <v>391014</v>
+      </c>
+      <c r="I32">
+        <v>3137695</v>
+      </c>
+      <c r="J32">
+        <v>83004</v>
+      </c>
+      <c r="K32">
+        <v>329.1</v>
+      </c>
+      <c r="L32">
         <v>0</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="M32">
+        <v>3620613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>45535</v>
       </c>
       <c r="B33">
-        <v>126502</v>
+        <v>844858</v>
       </c>
       <c r="C33">
-        <v>164.8</v>
+        <v>16924786</v>
       </c>
       <c r="D33">
-        <v>1109885</v>
+        <v>83.5</v>
       </c>
       <c r="E33">
-        <v>3155182</v>
+        <v>6051421</v>
       </c>
       <c r="F33">
-        <v>545782</v>
+        <v>12947388</v>
       </c>
       <c r="G33">
-        <v>118.2</v>
+        <v>3043249</v>
       </c>
       <c r="H33">
+        <v>13208711</v>
+      </c>
+      <c r="I33">
+        <v>7247458</v>
+      </c>
+      <c r="J33">
+        <v>175487</v>
+      </c>
+      <c r="K33">
+        <v>308.7</v>
+      </c>
+      <c r="L33">
         <v>0</v>
       </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="M33">
+        <v>3686673</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
         <v>45565</v>
       </c>
       <c r="B34">
-        <v>133926</v>
+        <v>972853</v>
       </c>
       <c r="C34">
-        <v>123.4</v>
+        <v>17001120</v>
       </c>
       <c r="D34">
-        <v>1531840</v>
+        <v>85.2</v>
       </c>
       <c r="E34">
-        <v>2807525</v>
+        <v>6541831</v>
       </c>
       <c r="F34">
-        <v>425066</v>
+        <v>14760408</v>
       </c>
       <c r="G34">
-        <v>67.7</v>
+        <v>5093714</v>
       </c>
       <c r="H34">
-        <v>0.27</v>
+        <v>21928902</v>
       </c>
       <c r="I34">
+        <v>8705458</v>
+      </c>
+      <c r="J34">
+        <v>216473</v>
+      </c>
+      <c r="K34">
+        <v>234.7</v>
+      </c>
+      <c r="L34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="M34">
+        <v>3944492</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
         <v>45596</v>
       </c>
       <c r="B35">
-        <v>113460</v>
+        <v>1051972</v>
       </c>
       <c r="C35">
-        <v>228.9</v>
+        <v>24934121</v>
       </c>
       <c r="D35">
-        <v>1082395</v>
+        <v>119.5</v>
       </c>
       <c r="E35">
-        <v>3016475</v>
+        <v>108453</v>
       </c>
       <c r="F35">
-        <v>310076</v>
+        <v>225618</v>
       </c>
       <c r="G35">
-        <v>330.3</v>
+        <v>2369673</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>11043196</v>
       </c>
       <c r="I35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>3314546</v>
+      </c>
+      <c r="J35">
+        <v>83993</v>
+      </c>
+      <c r="K35">
+        <v>160.2</v>
+      </c>
+      <c r="L35">
+        <v>1.96</v>
+      </c>
+      <c r="M35">
+        <v>4451358</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
         <v>45626</v>
       </c>
       <c r="B36">
-        <v>148296</v>
+        <v>1122183</v>
       </c>
       <c r="C36">
-        <v>289</v>
+        <v>606803</v>
       </c>
       <c r="D36">
-        <v>486351</v>
+        <v>2.9</v>
       </c>
       <c r="E36">
-        <v>1551924</v>
+        <v>5605424</v>
       </c>
       <c r="F36">
-        <v>525542</v>
+        <v>12286943</v>
       </c>
       <c r="G36">
-        <v>119.5</v>
+        <v>2049491</v>
       </c>
       <c r="H36">
-        <v>4.88</v>
+        <v>9216122</v>
       </c>
       <c r="I36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>8249657</v>
+      </c>
+      <c r="J36">
+        <v>209122</v>
+      </c>
+      <c r="K36">
+        <v>223.3</v>
+      </c>
+      <c r="L36">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="M36">
+        <v>4741015</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
         <v>45657</v>
       </c>
       <c r="B37">
-        <v>139222</v>
+        <v>1064952</v>
       </c>
       <c r="C37">
-        <v>85.5</v>
+        <v>215920</v>
       </c>
       <c r="D37">
-        <v>520855</v>
+        <v>1.1</v>
       </c>
       <c r="E37">
-        <v>1813934</v>
+        <v>2925725</v>
       </c>
       <c r="F37">
-        <v>422743</v>
+        <v>6648798</v>
       </c>
       <c r="G37">
-        <v>154.5</v>
+        <v>4919510</v>
       </c>
       <c r="H37">
-        <v>6.36</v>
+        <v>20288076</v>
       </c>
       <c r="I37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>166271</v>
+      </c>
+      <c r="J37">
+        <v>4118</v>
+      </c>
+      <c r="K37">
+        <v>86.7</v>
+      </c>
+      <c r="L37">
+        <v>8.01</v>
+      </c>
+      <c r="M37">
+        <v>4991588</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
         <v>45688</v>
       </c>
       <c r="B38">
-        <v>144283</v>
+        <v>1175969</v>
       </c>
       <c r="C38">
-        <v>141</v>
+        <v>16912308</v>
       </c>
       <c r="D38">
-        <v>887866</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E38">
-        <v>4459717</v>
+        <v>4925215</v>
       </c>
       <c r="F38">
-        <v>840026</v>
+        <v>10537609</v>
       </c>
       <c r="G38">
-        <v>230.8</v>
+        <v>3382009</v>
       </c>
       <c r="H38">
-        <v>7.42</v>
+        <v>15502876</v>
       </c>
       <c r="I38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>4199825</v>
+      </c>
+      <c r="J38">
+        <v>103942</v>
+      </c>
+      <c r="K38">
+        <v>160.9</v>
+      </c>
+      <c r="L38">
+        <v>14.6</v>
+      </c>
+      <c r="M38">
+        <v>5160294</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
         <v>45716</v>
       </c>
       <c r="B39">
-        <v>138127</v>
+        <v>1098292</v>
       </c>
       <c r="C39">
-        <v>173.4</v>
+        <v>360959</v>
       </c>
       <c r="D39">
-        <v>400167</v>
+        <v>1.8</v>
       </c>
       <c r="E39">
-        <v>1246117</v>
+        <v>2666447</v>
       </c>
       <c r="F39">
-        <v>463600</v>
+        <v>5495319</v>
       </c>
       <c r="G39">
-        <v>174.2</v>
+        <v>7581146</v>
       </c>
       <c r="H39">
-        <v>11.8</v>
+        <v>33454411</v>
       </c>
       <c r="I39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>6747593</v>
+      </c>
+      <c r="J39">
+        <v>163541</v>
+      </c>
+      <c r="K39">
+        <v>271.8</v>
+      </c>
+      <c r="L39">
+        <v>6.28</v>
+      </c>
+      <c r="M39">
+        <v>5090208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
         <v>45747</v>
       </c>
       <c r="B40">
-        <v>131931</v>
+        <v>1087844</v>
       </c>
       <c r="C40">
-        <v>207.1</v>
+        <v>23368568</v>
       </c>
       <c r="D40">
-        <v>2347445</v>
+        <v>115.1</v>
       </c>
       <c r="E40">
-        <v>2302990</v>
+        <v>5356484</v>
       </c>
       <c r="F40">
-        <v>305218</v>
+        <v>11499563</v>
       </c>
       <c r="G40">
-        <v>70.59999999999999</v>
+        <v>4370732</v>
       </c>
       <c r="H40">
-        <v>0.6899999999999999</v>
+        <v>18807261</v>
       </c>
       <c r="I40">
+        <v>1655141</v>
+      </c>
+      <c r="J40">
+        <v>38473</v>
+      </c>
+      <c r="K40">
+        <v>61.7</v>
+      </c>
+      <c r="L40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="M40">
+        <v>4849754</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
         <v>45777</v>
       </c>
       <c r="B41">
-        <v>126797</v>
+        <v>1049343</v>
       </c>
       <c r="C41">
-        <v>111.7</v>
+        <v>12193342</v>
       </c>
       <c r="D41">
-        <v>717476</v>
+        <v>59</v>
       </c>
       <c r="E41">
-        <v>2122740</v>
+        <v>1773404</v>
       </c>
       <c r="F41">
-        <v>283930</v>
+        <v>3788797</v>
       </c>
       <c r="G41">
-        <v>93</v>
+        <v>2527397</v>
       </c>
       <c r="H41">
-        <v>3.79</v>
+        <v>10785510</v>
       </c>
       <c r="I41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>6325875</v>
+      </c>
+      <c r="J41">
+        <v>157050</v>
+      </c>
+      <c r="K41">
+        <v>48</v>
+      </c>
+      <c r="L41">
+        <v>1.34</v>
+      </c>
+      <c r="M41">
+        <v>4529589</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
         <v>45808</v>
       </c>
       <c r="B42">
-        <v>121718</v>
+        <v>712617</v>
       </c>
       <c r="C42">
-        <v>27.3</v>
+        <v>61608</v>
       </c>
       <c r="D42">
-        <v>586282</v>
+        <v>0.3</v>
       </c>
       <c r="E42">
-        <v>1085472</v>
+        <v>2584648</v>
       </c>
       <c r="F42">
-        <v>195272</v>
+        <v>5521358</v>
       </c>
       <c r="G42">
-        <v>81</v>
+        <v>2501704</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>10216315</v>
       </c>
       <c r="I42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>2932883</v>
+      </c>
+      <c r="J42">
+        <v>66527</v>
+      </c>
+      <c r="K42">
+        <v>547.2</v>
+      </c>
+      <c r="L42">
+        <v>2.92</v>
+      </c>
+      <c r="M42">
+        <v>3911819</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
         <v>45838</v>
       </c>
       <c r="B43">
-        <v>110524</v>
+        <v>814631</v>
       </c>
       <c r="C43">
-        <v>92.40000000000001</v>
+        <v>12073364</v>
       </c>
       <c r="D43">
-        <v>1135371</v>
+        <v>60.4</v>
       </c>
       <c r="E43">
-        <v>1661983</v>
+        <v>1711769</v>
       </c>
       <c r="F43">
-        <v>225267</v>
+        <v>3991919</v>
       </c>
       <c r="G43">
-        <v>256.6</v>
+        <v>29498</v>
       </c>
       <c r="H43">
+        <v>132454</v>
+      </c>
+      <c r="I43">
+        <v>5638234</v>
+      </c>
+      <c r="J43">
+        <v>149055</v>
+      </c>
+      <c r="K43">
+        <v>39.4</v>
+      </c>
+      <c r="L43">
         <v>0</v>
       </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="M43">
+        <v>3687790</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
         <v>45869</v>
       </c>
       <c r="B44">
-        <v>119213</v>
+        <v>888121</v>
       </c>
       <c r="C44">
-        <v>294.6</v>
+        <v>31350866</v>
       </c>
       <c r="D44">
-        <v>1613095</v>
+        <v>147.8</v>
       </c>
       <c r="E44">
-        <v>2918526</v>
+        <v>2760258</v>
       </c>
       <c r="F44">
-        <v>258338</v>
+        <v>5648564</v>
       </c>
       <c r="G44">
-        <v>113.5</v>
+        <v>2227971</v>
       </c>
       <c r="H44">
+        <v>9637449</v>
+      </c>
+      <c r="I44">
+        <v>7484237</v>
+      </c>
+      <c r="J44">
+        <v>184480</v>
+      </c>
+      <c r="K44">
+        <v>74.8</v>
+      </c>
+      <c r="L44">
         <v>0</v>
       </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="M44">
+        <v>3542051</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
         <v>45900</v>
       </c>
       <c r="B45">
-        <v>118613</v>
+        <v>785866</v>
       </c>
       <c r="C45">
-        <v>61.7</v>
+        <v>172380</v>
       </c>
       <c r="D45">
-        <v>443048</v>
+        <v>0.8</v>
       </c>
       <c r="E45">
-        <v>1896755</v>
+        <v>2596862</v>
       </c>
       <c r="F45">
-        <v>237670</v>
+        <v>5314603</v>
       </c>
       <c r="G45">
-        <v>120.8</v>
+        <v>2274301</v>
       </c>
       <c r="H45">
+        <v>9619863</v>
+      </c>
+      <c r="I45">
+        <v>3813825</v>
+      </c>
+      <c r="J45">
+        <v>96421</v>
+      </c>
+      <c r="K45">
+        <v>214.8</v>
+      </c>
+      <c r="L45">
         <v>0</v>
       </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="M45">
+        <v>3649431</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
         <v>45930</v>
       </c>
       <c r="B46">
-        <v>103683</v>
+        <v>835408</v>
       </c>
       <c r="C46">
-        <v>90.3</v>
+        <v>192089</v>
       </c>
       <c r="D46">
-        <v>313368</v>
+        <v>0.9</v>
       </c>
       <c r="E46">
-        <v>2613845</v>
+        <v>122227</v>
       </c>
       <c r="F46">
-        <v>153274</v>
+        <v>247117</v>
       </c>
       <c r="G46">
-        <v>310.7</v>
+        <v>2075024</v>
       </c>
       <c r="H46">
+        <v>8851738</v>
+      </c>
+      <c r="I46">
+        <v>6516401</v>
+      </c>
+      <c r="J46">
+        <v>154903</v>
+      </c>
+      <c r="K46">
+        <v>167.9</v>
+      </c>
+      <c r="L46">
         <v>0</v>
       </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="M46">
+        <v>4183434</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
         <v>45961</v>
       </c>
       <c r="B47">
-        <v>110088</v>
+        <v>854119</v>
       </c>
       <c r="C47">
-        <v>73.09999999999999</v>
+        <v>10016874</v>
       </c>
       <c r="D47">
-        <v>1335610</v>
+        <v>48.4</v>
       </c>
       <c r="E47">
-        <v>2792004</v>
+        <v>6985143</v>
       </c>
       <c r="F47">
-        <v>186173</v>
+        <v>14517800</v>
       </c>
       <c r="G47">
-        <v>337.2</v>
+        <v>1032161</v>
       </c>
       <c r="H47">
+        <v>4467850</v>
+      </c>
+      <c r="I47">
+        <v>103041</v>
+      </c>
+      <c r="J47">
+        <v>2584</v>
+      </c>
+      <c r="K47">
+        <v>89</v>
+      </c>
+      <c r="L47">
         <v>0</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="M47">
+        <v>4353342</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
         <v>45991</v>
       </c>
       <c r="B48">
-        <v>136702</v>
+        <v>999506</v>
       </c>
       <c r="C48">
-        <v>288.9</v>
+        <v>31567683</v>
       </c>
       <c r="D48">
-        <v>1742912</v>
+        <v>146.8</v>
       </c>
       <c r="E48">
-        <v>3607392</v>
+        <v>7941652</v>
       </c>
       <c r="F48">
-        <v>266888</v>
+        <v>16610020</v>
       </c>
       <c r="G48">
-        <v>228.7</v>
+        <v>1742496</v>
       </c>
       <c r="H48">
-        <v>4.06</v>
+        <v>7415277</v>
       </c>
       <c r="I48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>65376</v>
+      </c>
+      <c r="J48">
+        <v>1608</v>
+      </c>
+      <c r="K48">
+        <v>312.1</v>
+      </c>
+      <c r="L48">
+        <v>4.57</v>
+      </c>
+      <c r="M48">
+        <v>4876489</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
         <v>46022</v>
       </c>
       <c r="B49">
-        <v>169710</v>
+        <v>1239183</v>
       </c>
       <c r="C49">
-        <v>296.5</v>
+        <v>30135168</v>
       </c>
       <c r="D49">
-        <v>2490256</v>
+        <v>141.2</v>
       </c>
       <c r="E49">
-        <v>4603399</v>
+        <v>145918</v>
       </c>
       <c r="F49">
-        <v>280892</v>
+        <v>307968</v>
       </c>
       <c r="G49">
-        <v>104.1</v>
+        <v>2231493</v>
       </c>
       <c r="H49">
-        <v>9.34</v>
+        <v>9685626</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>5732487</v>
+      </c>
+      <c r="J49">
+        <v>136840</v>
+      </c>
+      <c r="K49">
+        <v>115.7</v>
+      </c>
+      <c r="L49">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="M49">
+        <v>5008668</v>
       </c>
     </row>
   </sheetData>

--- a/static/sample-data/synth_otc_pharma.xlsx
+++ b/static/sample-data/synth_otc_pharma.xlsx
@@ -437,13 +437,13 @@
         <v>44592</v>
       </c>
       <c r="B2">
-        <v>1070757</v>
+        <v>1037734</v>
       </c>
       <c r="C2">
-        <v>22144623</v>
+        <v>28625903</v>
       </c>
       <c r="D2">
-        <v>127.1</v>
+        <v>164.2</v>
       </c>
       <c r="E2">
         <v>3023063</v>
@@ -452,16 +452,16 @@
         <v>8051534</v>
       </c>
       <c r="G2">
-        <v>1651420</v>
+        <v>1325462</v>
       </c>
       <c r="H2">
-        <v>7882354</v>
+        <v>6326531</v>
       </c>
       <c r="I2">
-        <v>3728343</v>
+        <v>1517414</v>
       </c>
       <c r="J2">
-        <v>106585</v>
+        <v>43379</v>
       </c>
       <c r="K2">
         <v>209.8</v>
@@ -470,7 +470,7 @@
         <v>3.07</v>
       </c>
       <c r="M2">
-        <v>5016366</v>
+        <v>4942859</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -478,13 +478,13 @@
         <v>44620</v>
       </c>
       <c r="B3">
-        <v>1084946</v>
+        <v>1054785</v>
       </c>
       <c r="C3">
-        <v>7412222</v>
+        <v>9838960</v>
       </c>
       <c r="D3">
-        <v>40.7</v>
+        <v>54.1</v>
       </c>
       <c r="E3">
         <v>5691435</v>
@@ -493,16 +493,16 @@
         <v>14045969</v>
       </c>
       <c r="G3">
-        <v>1053042</v>
+        <v>846495</v>
       </c>
       <c r="H3">
-        <v>5116459</v>
+        <v>4112899</v>
       </c>
       <c r="I3">
-        <v>3110262</v>
+        <v>1294448</v>
       </c>
       <c r="J3">
-        <v>85710</v>
+        <v>35671</v>
       </c>
       <c r="K3">
         <v>150.3</v>
@@ -511,7 +511,7 @@
         <v>7.54</v>
       </c>
       <c r="M3">
-        <v>4937246</v>
+        <v>4864898</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -519,13 +519,13 @@
         <v>44651</v>
       </c>
       <c r="B4">
-        <v>930908</v>
+        <v>941602</v>
       </c>
       <c r="C4">
-        <v>7101389</v>
+        <v>9448301</v>
       </c>
       <c r="D4">
-        <v>39.4</v>
+        <v>52.4</v>
       </c>
       <c r="E4">
         <v>2921811</v>
@@ -534,16 +534,16 @@
         <v>7457821</v>
       </c>
       <c r="G4">
-        <v>27064</v>
+        <v>21732</v>
       </c>
       <c r="H4">
-        <v>139028</v>
+        <v>111638</v>
       </c>
       <c r="I4">
-        <v>122542</v>
+        <v>49371</v>
       </c>
       <c r="J4">
-        <v>3528</v>
+        <v>1421</v>
       </c>
       <c r="K4">
         <v>90.2</v>
@@ -552,7 +552,7 @@
         <v>3.98</v>
       </c>
       <c r="M4">
-        <v>4533700</v>
+        <v>4467266</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -560,13 +560,13 @@
         <v>44681</v>
       </c>
       <c r="B5">
-        <v>984648</v>
+        <v>950883</v>
       </c>
       <c r="C5">
-        <v>26740913</v>
+        <v>34455044</v>
       </c>
       <c r="D5">
-        <v>148.7</v>
+        <v>191.6</v>
       </c>
       <c r="E5">
         <v>94837</v>
@@ -575,16 +575,16 @@
         <v>236555</v>
       </c>
       <c r="G5">
-        <v>2793323</v>
+        <v>2275705</v>
       </c>
       <c r="H5">
-        <v>13988333</v>
+        <v>11396222</v>
       </c>
       <c r="I5">
-        <v>7177972</v>
+        <v>2881975</v>
       </c>
       <c r="J5">
-        <v>198586</v>
+        <v>79733</v>
       </c>
       <c r="K5">
         <v>481.5</v>
@@ -593,7 +593,7 @@
         <v>4.78</v>
       </c>
       <c r="M5">
-        <v>4147856</v>
+        <v>4087075</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -601,13 +601,13 @@
         <v>44712</v>
       </c>
       <c r="B6">
-        <v>943398</v>
+        <v>908920</v>
       </c>
       <c r="C6">
-        <v>15098334</v>
+        <v>19544685</v>
       </c>
       <c r="D6">
-        <v>82.09999999999999</v>
+        <v>106.3</v>
       </c>
       <c r="E6">
         <v>50156</v>
@@ -616,16 +616,16 @@
         <v>126757</v>
       </c>
       <c r="G6">
-        <v>3759287</v>
+        <v>3071386</v>
       </c>
       <c r="H6">
-        <v>18293049</v>
+        <v>14945658</v>
       </c>
       <c r="I6">
-        <v>5681701</v>
+        <v>2295423</v>
       </c>
       <c r="J6">
-        <v>170047</v>
+        <v>68699</v>
       </c>
       <c r="K6">
         <v>124.2</v>
@@ -634,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>3704275</v>
+        <v>3649995</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -642,13 +642,13 @@
         <v>44742</v>
       </c>
       <c r="B7">
-        <v>807316</v>
+        <v>806927</v>
       </c>
       <c r="C7">
-        <v>12796587</v>
+        <v>16773185</v>
       </c>
       <c r="D7">
-        <v>73</v>
+        <v>95.7</v>
       </c>
       <c r="E7">
         <v>39127</v>
@@ -657,16 +657,16 @@
         <v>98886</v>
       </c>
       <c r="G7">
-        <v>928709</v>
+        <v>754710</v>
       </c>
       <c r="H7">
-        <v>4719228</v>
+        <v>3835049</v>
       </c>
       <c r="I7">
-        <v>2312561</v>
+        <v>940902</v>
       </c>
       <c r="J7">
-        <v>69992</v>
+        <v>28477</v>
       </c>
       <c r="K7">
         <v>171.3</v>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>3624774</v>
+        <v>3571658</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -683,13 +683,13 @@
         <v>44773</v>
       </c>
       <c r="B8">
-        <v>862777</v>
+        <v>852451</v>
       </c>
       <c r="C8">
-        <v>19787059</v>
+        <v>25530902</v>
       </c>
       <c r="D8">
-        <v>113.3</v>
+        <v>146.2</v>
       </c>
       <c r="E8">
         <v>918590</v>
@@ -698,16 +698,16 @@
         <v>2319774</v>
       </c>
       <c r="G8">
-        <v>2430470</v>
+        <v>1977466</v>
       </c>
       <c r="H8">
-        <v>11847177</v>
+        <v>9639038</v>
       </c>
       <c r="I8">
-        <v>4559676</v>
+        <v>1837339</v>
       </c>
       <c r="J8">
-        <v>125033</v>
+        <v>50382</v>
       </c>
       <c r="K8">
         <v>95.8</v>
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>3209504</v>
+        <v>3162474</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -724,13 +724,13 @@
         <v>44804</v>
       </c>
       <c r="B9">
-        <v>872523</v>
+        <v>825976</v>
       </c>
       <c r="C9">
-        <v>7526403</v>
+        <v>9846326</v>
       </c>
       <c r="D9">
-        <v>45</v>
+        <v>58.8</v>
       </c>
       <c r="E9">
         <v>3473118</v>
@@ -739,16 +739,16 @@
         <v>8714548</v>
       </c>
       <c r="G9">
-        <v>2658345</v>
+        <v>2173724</v>
       </c>
       <c r="H9">
-        <v>12425365</v>
+        <v>10160197</v>
       </c>
       <c r="I9">
-        <v>8799150</v>
+        <v>3530845</v>
       </c>
       <c r="J9">
-        <v>250664</v>
+        <v>100584</v>
       </c>
       <c r="K9">
         <v>233.5</v>
@@ -757,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>3550196</v>
+        <v>3498173</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -765,13 +765,13 @@
         <v>44834</v>
       </c>
       <c r="B10">
-        <v>1040679</v>
+        <v>1002494</v>
       </c>
       <c r="C10">
-        <v>20322062</v>
+        <v>26425881</v>
       </c>
       <c r="D10">
-        <v>109.5</v>
+        <v>142.4</v>
       </c>
       <c r="E10">
         <v>3400779</v>
@@ -780,16 +780,16 @@
         <v>8347790</v>
       </c>
       <c r="G10">
-        <v>5420406</v>
+        <v>4432894</v>
       </c>
       <c r="H10">
-        <v>24738260</v>
+        <v>20231344</v>
       </c>
       <c r="I10">
-        <v>7109365</v>
+        <v>2870441</v>
       </c>
       <c r="J10">
-        <v>194130</v>
+        <v>78381</v>
       </c>
       <c r="K10">
         <v>37.2</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>3964533</v>
+        <v>3906439</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -806,13 +806,13 @@
         <v>44865</v>
       </c>
       <c r="B11">
-        <v>1134122</v>
+        <v>1078509</v>
       </c>
       <c r="C11">
-        <v>13577245</v>
+        <v>17638268</v>
       </c>
       <c r="D11">
-        <v>72.7</v>
+        <v>94.5</v>
       </c>
       <c r="E11">
         <v>5492891</v>
@@ -821,16 +821,16 @@
         <v>13521379</v>
       </c>
       <c r="G11">
-        <v>2595130</v>
+        <v>2089792</v>
       </c>
       <c r="H11">
-        <v>12248079</v>
+        <v>9863065</v>
       </c>
       <c r="I11">
-        <v>12132939</v>
+        <v>4854785</v>
       </c>
       <c r="J11">
-        <v>349912</v>
+        <v>140011</v>
       </c>
       <c r="K11">
         <v>79.8</v>
@@ -839,7 +839,7 @@
         <v>1.07</v>
       </c>
       <c r="M11">
-        <v>4220852</v>
+        <v>4159002</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -847,13 +847,13 @@
         <v>44895</v>
       </c>
       <c r="B12">
-        <v>1231771</v>
+        <v>1208455</v>
       </c>
       <c r="C12">
-        <v>36694546</v>
+        <v>47204585</v>
       </c>
       <c r="D12">
-        <v>196.1</v>
+        <v>252.2</v>
       </c>
       <c r="E12">
         <v>1665030</v>
@@ -862,16 +862,16 @@
         <v>3881790</v>
       </c>
       <c r="G12">
-        <v>1722759</v>
+        <v>1396935</v>
       </c>
       <c r="H12">
-        <v>8495225</v>
+        <v>6888528</v>
       </c>
       <c r="I12">
-        <v>6330409</v>
+        <v>2546784</v>
       </c>
       <c r="J12">
-        <v>178841</v>
+        <v>71950</v>
       </c>
       <c r="K12">
         <v>118.5</v>
@@ -880,7 +880,7 @@
         <v>4.27</v>
       </c>
       <c r="M12">
-        <v>4310613</v>
+        <v>4247447</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -888,13 +888,13 @@
         <v>44926</v>
       </c>
       <c r="B13">
-        <v>1222747</v>
+        <v>1235093</v>
       </c>
       <c r="C13">
-        <v>33036147</v>
+        <v>42534034</v>
       </c>
       <c r="D13">
-        <v>178.7</v>
+        <v>230</v>
       </c>
       <c r="E13">
         <v>4659486</v>
@@ -903,16 +903,16 @@
         <v>11001140</v>
       </c>
       <c r="G13">
-        <v>126219</v>
+        <v>103262</v>
       </c>
       <c r="H13">
-        <v>586071</v>
+        <v>479474</v>
       </c>
       <c r="I13">
-        <v>3514642</v>
+        <v>1416619</v>
       </c>
       <c r="J13">
-        <v>92768</v>
+        <v>37391</v>
       </c>
       <c r="K13">
         <v>272.3</v>
@@ -921,7 +921,7 @@
         <v>1.91</v>
       </c>
       <c r="M13">
-        <v>4899182</v>
+        <v>4827392</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -929,13 +929,13 @@
         <v>44957</v>
       </c>
       <c r="B14">
-        <v>1302619</v>
+        <v>1312637</v>
       </c>
       <c r="C14">
-        <v>19219707</v>
+        <v>25126743</v>
       </c>
       <c r="D14">
-        <v>98.59999999999999</v>
+        <v>128.9</v>
       </c>
       <c r="E14">
         <v>6681870</v>
@@ -944,16 +944,16 @@
         <v>15672879</v>
       </c>
       <c r="G14">
-        <v>5187574</v>
+        <v>4239192</v>
       </c>
       <c r="H14">
-        <v>25639471</v>
+        <v>20952116</v>
       </c>
       <c r="I14">
-        <v>3189373</v>
+        <v>1313779</v>
       </c>
       <c r="J14">
-        <v>86941</v>
+        <v>35813</v>
       </c>
       <c r="K14">
         <v>197.6</v>
@@ -962,7 +962,7 @@
         <v>5.65</v>
       </c>
       <c r="M14">
-        <v>5193009</v>
+        <v>5116913</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -970,13 +970,13 @@
         <v>44985</v>
       </c>
       <c r="B15">
-        <v>1352702</v>
+        <v>1316132</v>
       </c>
       <c r="C15">
-        <v>8800646</v>
+        <v>11505511</v>
       </c>
       <c r="D15">
-        <v>47.5</v>
+        <v>62</v>
       </c>
       <c r="E15">
         <v>8294334</v>
@@ -985,16 +985,16 @@
         <v>18943476</v>
       </c>
       <c r="G15">
-        <v>2388633</v>
+        <v>1953366</v>
       </c>
       <c r="H15">
-        <v>11495902</v>
+        <v>9401066</v>
       </c>
       <c r="I15">
-        <v>8733175</v>
+        <v>3517323</v>
       </c>
       <c r="J15">
-        <v>232327</v>
+        <v>93571</v>
       </c>
       <c r="K15">
         <v>52.1</v>
@@ -1003,7 +1003,7 @@
         <v>12.63</v>
       </c>
       <c r="M15">
-        <v>4992821</v>
+        <v>4919659</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1011,13 +1011,13 @@
         <v>45016</v>
       </c>
       <c r="B16">
-        <v>1140319</v>
+        <v>1127725</v>
       </c>
       <c r="C16">
-        <v>14290541</v>
+        <v>18581566</v>
       </c>
       <c r="D16">
-        <v>71.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E16">
         <v>186180</v>
@@ -1026,16 +1026,16 @@
         <v>447503</v>
       </c>
       <c r="G16">
-        <v>4910977</v>
+        <v>4013374</v>
       </c>
       <c r="H16">
-        <v>23682961</v>
+        <v>19354311</v>
       </c>
       <c r="I16">
-        <v>3353874</v>
+        <v>1380712</v>
       </c>
       <c r="J16">
-        <v>90515</v>
+        <v>37263</v>
       </c>
       <c r="K16">
         <v>178.4</v>
@@ -1044,7 +1044,7 @@
         <v>5.26</v>
       </c>
       <c r="M16">
-        <v>4461682</v>
+        <v>4396303</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1052,13 +1052,13 @@
         <v>45046</v>
       </c>
       <c r="B17">
-        <v>1024015</v>
+        <v>1012807</v>
       </c>
       <c r="C17">
-        <v>8343761</v>
+        <v>11120017</v>
       </c>
       <c r="D17">
-        <v>44</v>
+        <v>58.7</v>
       </c>
       <c r="E17">
         <v>4189584</v>
@@ -1067,16 +1067,16 @@
         <v>9741302</v>
       </c>
       <c r="G17">
-        <v>2248621</v>
+        <v>1829946</v>
       </c>
       <c r="H17">
-        <v>10652534</v>
+        <v>8669119</v>
       </c>
       <c r="I17">
-        <v>3470816</v>
+        <v>1432573</v>
       </c>
       <c r="J17">
-        <v>90194</v>
+        <v>37227</v>
       </c>
       <c r="K17">
         <v>110.4</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>4662684</v>
+        <v>4594359</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1093,13 +1093,13 @@
         <v>45077</v>
       </c>
       <c r="B18">
-        <v>882956</v>
+        <v>915213</v>
       </c>
       <c r="C18">
-        <v>14672483</v>
+        <v>19156871</v>
       </c>
       <c r="D18">
-        <v>78.40000000000001</v>
+        <v>102.3</v>
       </c>
       <c r="E18">
         <v>2949944</v>
@@ -1108,16 +1108,16 @@
         <v>7035862</v>
       </c>
       <c r="G18">
-        <v>2500488</v>
+        <v>2038113</v>
       </c>
       <c r="H18">
-        <v>11604860</v>
+        <v>9458960</v>
       </c>
       <c r="I18">
-        <v>110181</v>
+        <v>44168</v>
       </c>
       <c r="J18">
-        <v>3003</v>
+        <v>1204</v>
       </c>
       <c r="K18">
         <v>59.7</v>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>4023385</v>
+        <v>3964428</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1134,13 +1134,13 @@
         <v>45107</v>
       </c>
       <c r="B19">
-        <v>807146</v>
+        <v>858730</v>
       </c>
       <c r="C19">
-        <v>31849316</v>
+        <v>40973436</v>
       </c>
       <c r="D19">
-        <v>170.7</v>
+        <v>219.6</v>
       </c>
       <c r="E19">
         <v>1991623</v>
@@ -1149,16 +1149,16 @@
         <v>4874196</v>
       </c>
       <c r="G19">
-        <v>4820713</v>
+        <v>3936550</v>
       </c>
       <c r="H19">
-        <v>22241423</v>
+        <v>18162140</v>
       </c>
       <c r="I19">
-        <v>141082</v>
+        <v>56518</v>
       </c>
       <c r="J19">
-        <v>4129</v>
+        <v>1654</v>
       </c>
       <c r="K19">
         <v>268.9</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>3613825</v>
+        <v>3560870</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1175,13 +1175,13 @@
         <v>45138</v>
       </c>
       <c r="B20">
-        <v>970592</v>
+        <v>972394</v>
       </c>
       <c r="C20">
-        <v>25770351</v>
+        <v>33204999</v>
       </c>
       <c r="D20">
-        <v>136.3</v>
+        <v>175.6</v>
       </c>
       <c r="E20">
         <v>7612168</v>
@@ -1190,16 +1190,16 @@
         <v>17400154</v>
       </c>
       <c r="G20">
-        <v>2841162</v>
+        <v>2320039</v>
       </c>
       <c r="H20">
-        <v>13354598</v>
+        <v>10905110</v>
       </c>
       <c r="I20">
-        <v>4723498</v>
+        <v>1904792</v>
       </c>
       <c r="J20">
-        <v>131977</v>
+        <v>53221</v>
       </c>
       <c r="K20">
         <v>110.6</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>3877300</v>
+        <v>3820484</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1216,13 +1216,13 @@
         <v>45169</v>
       </c>
       <c r="B21">
-        <v>881269</v>
+        <v>893879</v>
       </c>
       <c r="C21">
-        <v>18580948</v>
+        <v>24082925</v>
       </c>
       <c r="D21">
-        <v>96.59999999999999</v>
+        <v>125.1</v>
       </c>
       <c r="E21">
         <v>2617931</v>
@@ -1231,16 +1231,16 @@
         <v>6359816</v>
       </c>
       <c r="G21">
-        <v>47168</v>
+        <v>38462</v>
       </c>
       <c r="H21">
-        <v>234501</v>
+        <v>191220</v>
       </c>
       <c r="I21">
-        <v>3458430</v>
+        <v>1406660</v>
       </c>
       <c r="J21">
-        <v>91953</v>
+        <v>37400</v>
       </c>
       <c r="K21">
         <v>217.2</v>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>3561377</v>
+        <v>3509190</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1257,13 +1257,13 @@
         <v>45199</v>
       </c>
       <c r="B22">
-        <v>896282</v>
+        <v>905108</v>
       </c>
       <c r="C22">
-        <v>24547142</v>
+        <v>31857619</v>
       </c>
       <c r="D22">
-        <v>119.2</v>
+        <v>154.7</v>
       </c>
       <c r="E22">
         <v>110979</v>
@@ -1272,16 +1272,16 @@
         <v>238660</v>
       </c>
       <c r="G22">
-        <v>1458080</v>
+        <v>1167313</v>
       </c>
       <c r="H22">
-        <v>6603759</v>
+        <v>5286856</v>
       </c>
       <c r="I22">
-        <v>4059103</v>
+        <v>1652661</v>
       </c>
       <c r="J22">
-        <v>106262</v>
+        <v>43265</v>
       </c>
       <c r="K22">
         <v>401.7</v>
@@ -1290,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>3668011</v>
+        <v>3614262</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1298,13 +1298,13 @@
         <v>45230</v>
       </c>
       <c r="B23">
-        <v>1196548</v>
+        <v>1175868</v>
       </c>
       <c r="C23">
-        <v>58229452</v>
+        <v>74917237</v>
       </c>
       <c r="D23">
-        <v>296.4</v>
+        <v>381.3</v>
       </c>
       <c r="E23">
         <v>2568462</v>
@@ -1313,16 +1313,16 @@
         <v>5517293</v>
       </c>
       <c r="G23">
-        <v>7130111</v>
+        <v>5832792</v>
       </c>
       <c r="H23">
-        <v>31998692</v>
+        <v>26176554</v>
       </c>
       <c r="I23">
-        <v>11047663</v>
+        <v>4434771</v>
       </c>
       <c r="J23">
-        <v>292743</v>
+        <v>117513</v>
       </c>
       <c r="K23">
         <v>195.4</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>4284966</v>
+        <v>4222176</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1339,13 +1339,13 @@
         <v>45260</v>
       </c>
       <c r="B24">
-        <v>1223240</v>
+        <v>1234431</v>
       </c>
       <c r="C24">
-        <v>16285607</v>
+        <v>21078718</v>
       </c>
       <c r="D24">
-        <v>81.2</v>
+        <v>105.1</v>
       </c>
       <c r="E24">
         <v>1219324</v>
@@ -1354,16 +1354,16 @@
         <v>2989570</v>
       </c>
       <c r="G24">
-        <v>2496139</v>
+        <v>2028635</v>
       </c>
       <c r="H24">
-        <v>11147586</v>
+        <v>9059743</v>
       </c>
       <c r="I24">
-        <v>2870936</v>
+        <v>1194518</v>
       </c>
       <c r="J24">
-        <v>72594</v>
+        <v>30205</v>
       </c>
       <c r="K24">
         <v>106.9</v>
@@ -1372,7 +1372,7 @@
         <v>5.45</v>
       </c>
       <c r="M24">
-        <v>4737504</v>
+        <v>4668083</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1380,13 +1380,13 @@
         <v>45291</v>
       </c>
       <c r="B25">
-        <v>1302099</v>
+        <v>1286172</v>
       </c>
       <c r="C25">
-        <v>36741453</v>
+        <v>47272436</v>
       </c>
       <c r="D25">
-        <v>181.4</v>
+        <v>233.3</v>
       </c>
       <c r="E25">
         <v>80799</v>
@@ -1395,16 +1395,16 @@
         <v>179588</v>
       </c>
       <c r="G25">
-        <v>1589706</v>
+        <v>1277490</v>
       </c>
       <c r="H25">
-        <v>7400681</v>
+        <v>5947200</v>
       </c>
       <c r="I25">
-        <v>8589157</v>
+        <v>3453386</v>
       </c>
       <c r="J25">
-        <v>228215</v>
+        <v>91757</v>
       </c>
       <c r="K25">
         <v>151.4</v>
@@ -1413,7 +1413,7 @@
         <v>4.15</v>
       </c>
       <c r="M25">
-        <v>4712082</v>
+        <v>4643034</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1421,13 +1421,13 @@
         <v>45322</v>
       </c>
       <c r="B26">
-        <v>1403636</v>
+        <v>1385703</v>
       </c>
       <c r="C26">
-        <v>34418940</v>
+        <v>44254040</v>
       </c>
       <c r="D26">
-        <v>171.7</v>
+        <v>220.7</v>
       </c>
       <c r="E26">
         <v>54417</v>
@@ -1436,16 +1436,16 @@
         <v>127027</v>
       </c>
       <c r="G26">
-        <v>1599669</v>
+        <v>1305500</v>
       </c>
       <c r="H26">
-        <v>7306026</v>
+        <v>5962494</v>
       </c>
       <c r="I26">
-        <v>8501056</v>
+        <v>3432726</v>
       </c>
       <c r="J26">
-        <v>228964</v>
+        <v>92456</v>
       </c>
       <c r="K26">
         <v>72.5</v>
@@ -1454,7 +1454,7 @@
         <v>12.47</v>
       </c>
       <c r="M26">
-        <v>5287540</v>
+        <v>5210059</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1462,13 +1462,13 @@
         <v>45351</v>
       </c>
       <c r="B27">
-        <v>1170302</v>
+        <v>1210133</v>
       </c>
       <c r="C27">
-        <v>10388696</v>
+        <v>13803087</v>
       </c>
       <c r="D27">
-        <v>49.4</v>
+        <v>65.7</v>
       </c>
       <c r="E27">
         <v>2398469</v>
@@ -1477,16 +1477,16 @@
         <v>5344893</v>
       </c>
       <c r="G27">
-        <v>3017606</v>
+        <v>2460433</v>
       </c>
       <c r="H27">
-        <v>13844390</v>
+        <v>11288154</v>
       </c>
       <c r="I27">
-        <v>197563</v>
+        <v>79087</v>
       </c>
       <c r="J27">
-        <v>4984</v>
+        <v>1995</v>
       </c>
       <c r="K27">
         <v>303.7</v>
@@ -1495,7 +1495,7 @@
         <v>7.49</v>
       </c>
       <c r="M27">
-        <v>5243526</v>
+        <v>5166690</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1503,13 +1503,13 @@
         <v>45382</v>
       </c>
       <c r="B28">
-        <v>1206278</v>
+        <v>1176809</v>
       </c>
       <c r="C28">
-        <v>15886715</v>
+        <v>20959105</v>
       </c>
       <c r="D28">
-        <v>80.5</v>
+        <v>106.2</v>
       </c>
       <c r="E28">
         <v>6135648</v>
@@ -1518,16 +1518,16 @@
         <v>13775344</v>
       </c>
       <c r="G28">
-        <v>4076384</v>
+        <v>3325705</v>
       </c>
       <c r="H28">
-        <v>17914373</v>
+        <v>14615386</v>
       </c>
       <c r="I28">
-        <v>8877100</v>
+        <v>3561568</v>
       </c>
       <c r="J28">
-        <v>233849</v>
+        <v>93822</v>
       </c>
       <c r="K28">
         <v>170.4</v>
@@ -1536,7 +1536,7 @@
         <v>3.45</v>
       </c>
       <c r="M28">
-        <v>4484401</v>
+        <v>4418689</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1544,13 +1544,13 @@
         <v>45412</v>
       </c>
       <c r="B29">
-        <v>1034758</v>
+        <v>1019954</v>
       </c>
       <c r="C29">
-        <v>20730794</v>
+        <v>26744305</v>
       </c>
       <c r="D29">
-        <v>105.6</v>
+        <v>136.2</v>
       </c>
       <c r="E29">
         <v>3665787</v>
@@ -1559,16 +1559,16 @@
         <v>8926289</v>
       </c>
       <c r="G29">
-        <v>2627799</v>
+        <v>2147272</v>
       </c>
       <c r="H29">
-        <v>12508594</v>
+        <v>10221237</v>
       </c>
       <c r="I29">
-        <v>5473182</v>
+        <v>2215037</v>
       </c>
       <c r="J29">
-        <v>139643</v>
+        <v>56515</v>
       </c>
       <c r="K29">
         <v>464.5</v>
@@ -1577,7 +1577,7 @@
         <v>4.72</v>
       </c>
       <c r="M29">
-        <v>4241984</v>
+        <v>4179824</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1585,13 +1585,13 @@
         <v>45443</v>
       </c>
       <c r="B30">
-        <v>899792</v>
+        <v>897679</v>
       </c>
       <c r="C30">
-        <v>7674393</v>
+        <v>10119271</v>
       </c>
       <c r="D30">
-        <v>39.6</v>
+        <v>52.3</v>
       </c>
       <c r="E30">
         <v>38697</v>
@@ -1600,16 +1600,16 @@
         <v>86432</v>
       </c>
       <c r="G30">
-        <v>36883</v>
+        <v>29730</v>
       </c>
       <c r="H30">
-        <v>167484</v>
+        <v>134998</v>
       </c>
       <c r="I30">
-        <v>3326099</v>
+        <v>1336725</v>
       </c>
       <c r="J30">
-        <v>89046</v>
+        <v>35787</v>
       </c>
       <c r="K30">
         <v>176.6</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>3760638</v>
+        <v>3705531</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1626,13 +1626,13 @@
         <v>45473</v>
       </c>
       <c r="B31">
-        <v>847066</v>
+        <v>862859</v>
       </c>
       <c r="C31">
-        <v>19150850</v>
+        <v>24971139</v>
       </c>
       <c r="D31">
-        <v>97.7</v>
+        <v>127.4</v>
       </c>
       <c r="E31">
         <v>4119922</v>
@@ -1641,16 +1641,16 @@
         <v>9027621</v>
       </c>
       <c r="G31">
-        <v>5183506</v>
+        <v>4238985</v>
       </c>
       <c r="H31">
-        <v>22669850</v>
+        <v>18539029</v>
       </c>
       <c r="I31">
-        <v>2024986</v>
+        <v>831275</v>
       </c>
       <c r="J31">
-        <v>55181</v>
+        <v>22652</v>
       </c>
       <c r="K31">
         <v>192.8</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>3470538</v>
+        <v>3419683</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1667,13 +1667,13 @@
         <v>45504</v>
       </c>
       <c r="B32">
-        <v>722797</v>
+        <v>716748</v>
       </c>
       <c r="C32">
-        <v>2296537</v>
+        <v>2999556</v>
       </c>
       <c r="D32">
-        <v>12.4</v>
+        <v>16.1</v>
       </c>
       <c r="E32">
         <v>556981</v>
@@ -1682,16 +1682,16 @@
         <v>1254641</v>
       </c>
       <c r="G32">
-        <v>85009</v>
+        <v>69440</v>
       </c>
       <c r="H32">
-        <v>391014</v>
+        <v>319403</v>
       </c>
       <c r="I32">
-        <v>3137695</v>
+        <v>1295795</v>
       </c>
       <c r="J32">
-        <v>83004</v>
+        <v>34279</v>
       </c>
       <c r="K32">
         <v>329.1</v>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>3620613</v>
+        <v>3567559</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1708,13 +1708,13 @@
         <v>45535</v>
       </c>
       <c r="B33">
-        <v>844858</v>
+        <v>808786</v>
       </c>
       <c r="C33">
-        <v>16924786</v>
+        <v>21927697</v>
       </c>
       <c r="D33">
-        <v>83.5</v>
+        <v>108.1</v>
       </c>
       <c r="E33">
         <v>6051421</v>
@@ -1723,16 +1723,16 @@
         <v>12947388</v>
       </c>
       <c r="G33">
-        <v>3043249</v>
+        <v>2466894</v>
       </c>
       <c r="H33">
-        <v>13208711</v>
+        <v>10707138</v>
       </c>
       <c r="I33">
-        <v>7247458</v>
+        <v>2907578</v>
       </c>
       <c r="J33">
-        <v>175487</v>
+        <v>70403</v>
       </c>
       <c r="K33">
         <v>308.7</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>3686673</v>
+        <v>3632650</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1749,13 +1749,13 @@
         <v>45565</v>
       </c>
       <c r="B34">
-        <v>972853</v>
+        <v>928847</v>
       </c>
       <c r="C34">
-        <v>17001120</v>
+        <v>22552974</v>
       </c>
       <c r="D34">
-        <v>85.2</v>
+        <v>113</v>
       </c>
       <c r="E34">
         <v>6541831</v>
@@ -1764,16 +1764,16 @@
         <v>14760408</v>
       </c>
       <c r="G34">
-        <v>5093714</v>
+        <v>4154354</v>
       </c>
       <c r="H34">
-        <v>21928902</v>
+        <v>17884873</v>
       </c>
       <c r="I34">
-        <v>8705458</v>
+        <v>3501468</v>
       </c>
       <c r="J34">
-        <v>216473</v>
+        <v>87069</v>
       </c>
       <c r="K34">
         <v>234.7</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>3944492</v>
+        <v>3886692</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1790,13 +1790,13 @@
         <v>45596</v>
       </c>
       <c r="B35">
-        <v>1051972</v>
+        <v>1046413</v>
       </c>
       <c r="C35">
-        <v>24934121</v>
+        <v>32392104</v>
       </c>
       <c r="D35">
-        <v>119.5</v>
+        <v>155.3</v>
       </c>
       <c r="E35">
         <v>108453</v>
@@ -1805,16 +1805,16 @@
         <v>225618</v>
       </c>
       <c r="G35">
-        <v>2369673</v>
+        <v>1937909</v>
       </c>
       <c r="H35">
-        <v>11043196</v>
+        <v>9031083</v>
       </c>
       <c r="I35">
-        <v>3314546</v>
+        <v>1343732</v>
       </c>
       <c r="J35">
-        <v>83993</v>
+        <v>34051</v>
       </c>
       <c r="K35">
         <v>160.2</v>
@@ -1823,7 +1823,7 @@
         <v>1.96</v>
       </c>
       <c r="M35">
-        <v>4451358</v>
+        <v>4386130</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1831,13 +1831,13 @@
         <v>45626</v>
       </c>
       <c r="B36">
-        <v>1122183</v>
+        <v>1068465</v>
       </c>
       <c r="C36">
-        <v>606803</v>
+        <v>786089</v>
       </c>
       <c r="D36">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="E36">
         <v>5605424</v>
@@ -1846,16 +1846,16 @@
         <v>12286943</v>
       </c>
       <c r="G36">
-        <v>2049491</v>
+        <v>1668168</v>
       </c>
       <c r="H36">
-        <v>9216122</v>
+        <v>7501394</v>
       </c>
       <c r="I36">
-        <v>8249657</v>
+        <v>3313158</v>
       </c>
       <c r="J36">
-        <v>209122</v>
+        <v>83986</v>
       </c>
       <c r="K36">
         <v>223.3</v>
@@ -1864,7 +1864,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="M36">
-        <v>4741015</v>
+        <v>4671542</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1872,13 +1872,13 @@
         <v>45657</v>
       </c>
       <c r="B37">
-        <v>1064952</v>
+        <v>1055241</v>
       </c>
       <c r="C37">
-        <v>215920</v>
+        <v>284847</v>
       </c>
       <c r="D37">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="E37">
         <v>2925725</v>
@@ -1887,16 +1887,16 @@
         <v>6648798</v>
       </c>
       <c r="G37">
-        <v>4919510</v>
+        <v>4016998</v>
       </c>
       <c r="H37">
-        <v>20288076</v>
+        <v>16566113</v>
       </c>
       <c r="I37">
-        <v>166271</v>
+        <v>66595</v>
       </c>
       <c r="J37">
-        <v>4118</v>
+        <v>1649</v>
       </c>
       <c r="K37">
         <v>86.7</v>
@@ -1905,7 +1905,7 @@
         <v>8.01</v>
       </c>
       <c r="M37">
-        <v>4991588</v>
+        <v>4918443</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1913,13 +1913,13 @@
         <v>45688</v>
       </c>
       <c r="B38">
-        <v>1175969</v>
+        <v>1144489</v>
       </c>
       <c r="C38">
-        <v>16912308</v>
+        <v>22052617</v>
       </c>
       <c r="D38">
-        <v>76.90000000000001</v>
+        <v>100.3</v>
       </c>
       <c r="E38">
         <v>4925215</v>
@@ -1928,16 +1928,16 @@
         <v>10537609</v>
       </c>
       <c r="G38">
-        <v>3382009</v>
+        <v>2762455</v>
       </c>
       <c r="H38">
-        <v>15502876</v>
+        <v>12662887</v>
       </c>
       <c r="I38">
-        <v>4199825</v>
+        <v>1714196</v>
       </c>
       <c r="J38">
-        <v>103942</v>
+        <v>42425</v>
       </c>
       <c r="K38">
         <v>160.9</v>
@@ -1946,7 +1946,7 @@
         <v>14.6</v>
       </c>
       <c r="M38">
-        <v>5160294</v>
+        <v>5084678</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1954,13 +1954,13 @@
         <v>45716</v>
       </c>
       <c r="B39">
-        <v>1098292</v>
+        <v>1027482</v>
       </c>
       <c r="C39">
-        <v>360959</v>
+        <v>468213</v>
       </c>
       <c r="D39">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="E39">
         <v>2666447</v>
@@ -1969,16 +1969,16 @@
         <v>5495319</v>
       </c>
       <c r="G39">
-        <v>7581146</v>
+        <v>6196475</v>
       </c>
       <c r="H39">
-        <v>33454411</v>
+        <v>27344073</v>
       </c>
       <c r="I39">
-        <v>6747593</v>
+        <v>2721180</v>
       </c>
       <c r="J39">
-        <v>163541</v>
+        <v>65953</v>
       </c>
       <c r="K39">
         <v>271.8</v>
@@ -1987,7 +1987,7 @@
         <v>6.28</v>
       </c>
       <c r="M39">
-        <v>5090208</v>
+        <v>5015619</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1995,13 +1995,13 @@
         <v>45747</v>
       </c>
       <c r="B40">
-        <v>1087844</v>
+        <v>1085147</v>
       </c>
       <c r="C40">
-        <v>23368568</v>
+        <v>30517092</v>
       </c>
       <c r="D40">
-        <v>115.1</v>
+        <v>150.3</v>
       </c>
       <c r="E40">
         <v>5356484</v>
@@ -2010,16 +2010,16 @@
         <v>11499563</v>
       </c>
       <c r="G40">
-        <v>4370732</v>
+        <v>3560597</v>
       </c>
       <c r="H40">
-        <v>18807261</v>
+        <v>15321247</v>
       </c>
       <c r="I40">
-        <v>1655141</v>
+        <v>680544</v>
       </c>
       <c r="J40">
-        <v>38473</v>
+        <v>15819</v>
       </c>
       <c r="K40">
         <v>61.7</v>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>4849754</v>
+        <v>4778688</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2036,13 +2036,13 @@
         <v>45777</v>
       </c>
       <c r="B41">
-        <v>1049343</v>
+        <v>1008975</v>
       </c>
       <c r="C41">
-        <v>12193342</v>
+        <v>15856753</v>
       </c>
       <c r="D41">
-        <v>59</v>
+        <v>76.8</v>
       </c>
       <c r="E41">
         <v>1773404</v>
@@ -2051,16 +2051,16 @@
         <v>3788797</v>
       </c>
       <c r="G41">
-        <v>2527397</v>
+        <v>2062415</v>
       </c>
       <c r="H41">
-        <v>10785510</v>
+        <v>8801226</v>
       </c>
       <c r="I41">
-        <v>6325875</v>
+        <v>2568774</v>
       </c>
       <c r="J41">
-        <v>157050</v>
+        <v>63774</v>
       </c>
       <c r="K41">
         <v>48</v>
@@ -2069,7 +2069,7 @@
         <v>1.34</v>
       </c>
       <c r="M41">
-        <v>4529589</v>
+        <v>4463215</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2077,13 +2077,13 @@
         <v>45808</v>
       </c>
       <c r="B42">
-        <v>712617</v>
+        <v>685243</v>
       </c>
       <c r="C42">
-        <v>61608</v>
+        <v>80126</v>
       </c>
       <c r="D42">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E42">
         <v>2584648</v>
@@ -2092,16 +2092,16 @@
         <v>5521358</v>
       </c>
       <c r="G42">
-        <v>2501704</v>
+        <v>2039694</v>
       </c>
       <c r="H42">
-        <v>10216315</v>
+        <v>8329587</v>
       </c>
       <c r="I42">
-        <v>2932883</v>
+        <v>1192251</v>
       </c>
       <c r="J42">
-        <v>66527</v>
+        <v>27044</v>
       </c>
       <c r="K42">
         <v>547.2</v>
@@ -2110,7 +2110,7 @@
         <v>2.92</v>
       </c>
       <c r="M42">
-        <v>3911819</v>
+        <v>3854497</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2118,13 +2118,13 @@
         <v>45838</v>
       </c>
       <c r="B43">
-        <v>814631</v>
+        <v>772312</v>
       </c>
       <c r="C43">
-        <v>12073364</v>
+        <v>15958382</v>
       </c>
       <c r="D43">
-        <v>60.4</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E43">
         <v>1711769</v>
@@ -2133,16 +2133,16 @@
         <v>3991919</v>
       </c>
       <c r="G43">
-        <v>29498</v>
+        <v>24020</v>
       </c>
       <c r="H43">
-        <v>132454</v>
+        <v>107858</v>
       </c>
       <c r="I43">
-        <v>5638234</v>
+        <v>2270651</v>
       </c>
       <c r="J43">
-        <v>149055</v>
+        <v>60028</v>
       </c>
       <c r="K43">
         <v>39.4</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>3687790</v>
+        <v>3633751</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2159,13 +2159,13 @@
         <v>45869</v>
       </c>
       <c r="B44">
-        <v>888121</v>
+        <v>858112</v>
       </c>
       <c r="C44">
-        <v>31350866</v>
+        <v>40582683</v>
       </c>
       <c r="D44">
-        <v>147.8</v>
+        <v>191.3</v>
       </c>
       <c r="E44">
         <v>2760258</v>
@@ -2174,16 +2174,16 @@
         <v>5648564</v>
       </c>
       <c r="G44">
-        <v>2227971</v>
+        <v>1803764</v>
       </c>
       <c r="H44">
-        <v>9637449</v>
+        <v>7802472</v>
       </c>
       <c r="I44">
-        <v>7484237</v>
+        <v>2999814</v>
       </c>
       <c r="J44">
-        <v>184480</v>
+        <v>73943</v>
       </c>
       <c r="K44">
         <v>74.8</v>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>3542051</v>
+        <v>3490147</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2200,13 +2200,13 @@
         <v>45900</v>
       </c>
       <c r="B45">
-        <v>785866</v>
+        <v>756733</v>
       </c>
       <c r="C45">
-        <v>172380</v>
+        <v>228204</v>
       </c>
       <c r="D45">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="E45">
         <v>2596862</v>
@@ -2215,16 +2215,16 @@
         <v>5314603</v>
       </c>
       <c r="G45">
-        <v>2274301</v>
+        <v>1851537</v>
       </c>
       <c r="H45">
-        <v>9619863</v>
+        <v>7831652</v>
       </c>
       <c r="I45">
-        <v>3813825</v>
+        <v>1574725</v>
       </c>
       <c r="J45">
-        <v>96421</v>
+        <v>39812</v>
       </c>
       <c r="K45">
         <v>214.8</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>3649431</v>
+        <v>3595954</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2241,13 +2241,13 @@
         <v>45930</v>
       </c>
       <c r="B46">
-        <v>835408</v>
+        <v>774665</v>
       </c>
       <c r="C46">
-        <v>192089</v>
+        <v>248696</v>
       </c>
       <c r="D46">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="E46">
         <v>122227</v>
@@ -2256,16 +2256,16 @@
         <v>247117</v>
       </c>
       <c r="G46">
-        <v>2075024</v>
+        <v>1688348</v>
       </c>
       <c r="H46">
-        <v>8851738</v>
+        <v>7202234</v>
       </c>
       <c r="I46">
-        <v>6516401</v>
+        <v>2643890</v>
       </c>
       <c r="J46">
-        <v>154903</v>
+        <v>62848</v>
       </c>
       <c r="K46">
         <v>167.9</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <v>4183434</v>
+        <v>4122132</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2282,13 +2282,13 @@
         <v>45961</v>
       </c>
       <c r="B47">
-        <v>854119</v>
+        <v>857492</v>
       </c>
       <c r="C47">
-        <v>10016874</v>
+        <v>13251165</v>
       </c>
       <c r="D47">
-        <v>48.4</v>
+        <v>64</v>
       </c>
       <c r="E47">
         <v>6985143</v>
@@ -2297,16 +2297,16 @@
         <v>14517800</v>
       </c>
       <c r="G47">
-        <v>1032161</v>
+        <v>835904</v>
       </c>
       <c r="H47">
-        <v>4467850</v>
+        <v>3618327</v>
       </c>
       <c r="I47">
-        <v>103041</v>
+        <v>42391</v>
       </c>
       <c r="J47">
-        <v>2584</v>
+        <v>1063</v>
       </c>
       <c r="K47">
         <v>89</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>4353342</v>
+        <v>4289550</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2323,13 +2323,13 @@
         <v>45991</v>
       </c>
       <c r="B48">
-        <v>999506</v>
+        <v>1036649</v>
       </c>
       <c r="C48">
-        <v>31567683</v>
+        <v>40911039</v>
       </c>
       <c r="D48">
-        <v>146.8</v>
+        <v>190.2</v>
       </c>
       <c r="E48">
         <v>7941652</v>
@@ -2338,16 +2338,16 @@
         <v>16610020</v>
       </c>
       <c r="G48">
-        <v>1742496</v>
+        <v>1398004</v>
       </c>
       <c r="H48">
-        <v>7415277</v>
+        <v>5949276</v>
       </c>
       <c r="I48">
-        <v>65376</v>
+        <v>26947</v>
       </c>
       <c r="J48">
-        <v>1608</v>
+        <v>663</v>
       </c>
       <c r="K48">
         <v>312.1</v>
@@ -2356,7 +2356,7 @@
         <v>4.57</v>
       </c>
       <c r="M48">
-        <v>4876489</v>
+        <v>4805031</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2364,13 +2364,13 @@
         <v>46022</v>
       </c>
       <c r="B49">
-        <v>1239183</v>
+        <v>1230129</v>
       </c>
       <c r="C49">
-        <v>30135168</v>
+        <v>38821805</v>
       </c>
       <c r="D49">
-        <v>141.2</v>
+        <v>181.9</v>
       </c>
       <c r="E49">
         <v>145918</v>
@@ -2379,16 +2379,16 @@
         <v>307968</v>
       </c>
       <c r="G49">
-        <v>2231493</v>
+        <v>1818288</v>
       </c>
       <c r="H49">
-        <v>9685626</v>
+        <v>7892144</v>
       </c>
       <c r="I49">
-        <v>5732487</v>
+        <v>2317563</v>
       </c>
       <c r="J49">
-        <v>136840</v>
+        <v>55322</v>
       </c>
       <c r="K49">
         <v>115.7</v>
@@ -2397,7 +2397,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="M49">
-        <v>5008668</v>
+        <v>4935273</v>
       </c>
     </row>
   </sheetData>
